--- a/podaci/hcs-web-data.xlsx
+++ b/podaci/hcs-web-data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30522"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projekti\curling-hr\podaci\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projekti\curling-hr\podaci\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D7925EC-ED41-4356-BD13-DFFD4BF20A5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A25EA87-180C-4FFA-9E44-E25AC262C195}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{63D9C5CB-4420-4CCB-9E09-733AC492CE83}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="28296" windowHeight="15456" activeTab="1" xr2:uid="{63D9C5CB-4420-4CCB-9E09-733AC492CE83}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="2" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="622">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="648">
   <si>
     <t>Ivan Veštić</t>
   </si>
@@ -1643,9 +1643,6 @@
     <t>28. – 29.11.2026.</t>
   </si>
   <si>
-    <t>Prvenstvo Hrvatske za mješovite parove (seniori)</t>
-  </si>
-  <si>
     <t>06. – 07.02.2027.</t>
   </si>
   <si>
@@ -1664,9 +1661,6 @@
     <t>Lafayette, SAD</t>
   </si>
   <si>
-    <t>12. – 19.10.2026.</t>
-  </si>
-  <si>
     <t>World Mixed Curling Championship</t>
   </si>
   <si>
@@ -1682,18 +1676,12 @@
     <t>08. – 13.11.2026.</t>
   </si>
   <si>
-    <t>World Men Championship Qualifier</t>
-  </si>
-  <si>
     <t>Aberdeen, Škotska</t>
   </si>
   <si>
     <t>21. – 26.11.2026.</t>
   </si>
   <si>
-    <t>World Women Championship Qualifier</t>
-  </si>
-  <si>
     <t>Östersund, Švedska</t>
   </si>
   <si>
@@ -1736,9 +1724,6 @@
     <t>04/2027.</t>
   </si>
   <si>
-    <t>World Championship Pre-Qualifiers</t>
-  </si>
-  <si>
     <t>24.04. – 02.05.2027.</t>
   </si>
   <si>
@@ -1823,42 +1808,6 @@
     <t>00545886834</t>
   </si>
   <si>
-    <t>Prvenstvo Hrvatske za muškarce (juniori) - sezona 2025-2026</t>
-  </si>
-  <si>
-    <t>Prvenstvo Hrvatske za žene (juniorke) - sezona 2025-2026</t>
-  </si>
-  <si>
-    <t>Prvenstvo Hrvatske za žene (seniorke) - sezona 2025-2026</t>
-  </si>
-  <si>
-    <t>Prvenstvo Hrvatske za muškarce (juniori)</t>
-  </si>
-  <si>
-    <t>Prvenstvo Hrvatske za žene (juniorke)</t>
-  </si>
-  <si>
-    <t>Prvenstvo Hrvatske u mješovitom curlingu (seniori)</t>
-  </si>
-  <si>
-    <t>Prvenstvo Hrvatske za muškarce (seniori), termin 1</t>
-  </si>
-  <si>
-    <t>Prvenstvo Hrvatske za žene (seniorke), termin 1</t>
-  </si>
-  <si>
-    <t>Prvenstvo Hrvatske za mješovite parove (juniori)</t>
-  </si>
-  <si>
-    <t>Prvenstvo Hrvatske za muškarce (seniori), termin 2</t>
-  </si>
-  <si>
-    <t>Prvenstvo Hrvatske za žene (seniorke), termin 2</t>
-  </si>
-  <si>
-    <t>Prvenstvo Hrvatske u mješovitom curlingu (juniori)</t>
-  </si>
-  <si>
     <t>https://softpeelr.com/en/tournaments/</t>
   </si>
   <si>
@@ -1911,13 +1860,142 @@
   </si>
   <si>
     <t>Jedine nove stranice u pravilu će biti nove vijesti. Svaka vijest se sastoji od teksta i par fotografija. Za izradu i objavu takvih novih stranica vijesti treba otići na ../edit</t>
+  </si>
+  <si>
+    <t>HR</t>
+  </si>
+  <si>
+    <t>(HR)</t>
+  </si>
+  <si>
+    <t>Penticton, Kanada</t>
+  </si>
+  <si>
+    <t>03. – 10.04.2027.</t>
+  </si>
+  <si>
+    <t>World Championship Qualifier (Women)</t>
+  </si>
+  <si>
+    <t>World Championship Qualifier (Men)</t>
+  </si>
+  <si>
+    <t>World Championship Pre-Qualifiers (Men)</t>
+  </si>
+  <si>
+    <t>World Championship Pre-Qualifiers (Women)</t>
+  </si>
+  <si>
+    <t>Svjetsko prvenstvo za mješovite parove</t>
+  </si>
+  <si>
+    <t>Europsko prvenstvo za muškarce</t>
+  </si>
+  <si>
+    <t>Europsko prvenstvo za žene</t>
+  </si>
+  <si>
+    <t>Kvalifikacije za Svjetsko prvenstvo za mješovite parove</t>
+  </si>
+  <si>
+    <t>Kvalifikacije za Svjetsko prvenstvo za muškarce</t>
+  </si>
+  <si>
+    <t>Kvalifikacije za Svjetsko prvenstvo za žene</t>
+  </si>
+  <si>
+    <t>Juniori</t>
+  </si>
+  <si>
+    <t>Seniori</t>
+  </si>
+  <si>
+    <t>Veterani</t>
+  </si>
+  <si>
+    <t>Prvenstvo Hrvatske za muškarce - sezona 2025-2026</t>
+  </si>
+  <si>
+    <t>Prvenstvo Hrvatske za žene - sezona 2025-2026</t>
+  </si>
+  <si>
+    <t>Prvenstvo Hrvatske za muškarce</t>
+  </si>
+  <si>
+    <t>Prvenstvo Hrvatske za žene</t>
+  </si>
+  <si>
+    <t>Prvenstvo Hrvatske u mješovitom curlingu</t>
+  </si>
+  <si>
+    <t>Prvenstvo Hrvatske za mješovite parove</t>
+  </si>
+  <si>
+    <t>Prvenstvo Hrvatske za muškarce, termin 1</t>
+  </si>
+  <si>
+    <t>Prvenstvo Hrvatske za žene, termin 1</t>
+  </si>
+  <si>
+    <t>Prvenstvo Hrvatske za muškarce, termin 2</t>
+  </si>
+  <si>
+    <t>Prvenstvo Hrvatske za žene, termin 2</t>
+  </si>
+  <si>
+    <t>Svjetsko prvenstvo za muškarce</t>
+  </si>
+  <si>
+    <t>Svjetsko prvenstvo za žene</t>
+  </si>
+  <si>
+    <t>Svjetsko prvenstvo u mješovitom curlingu</t>
+  </si>
+  <si>
+    <t>Pretkvalifikacije za Svjetsko prvenstvo za muškarce</t>
+  </si>
+  <si>
+    <t>Pretkvalifikacije za Svjetsko prvenstvo za žene</t>
+  </si>
+  <si>
+    <t>Juniors</t>
+  </si>
+  <si>
+    <t>Seniors</t>
+  </si>
+  <si>
+    <t>Adults</t>
+  </si>
+  <si>
+    <t>Croatian Men Championship</t>
+  </si>
+  <si>
+    <t>Croatian Women Championship</t>
+  </si>
+  <si>
+    <t>Croatian Mixed Championship</t>
+  </si>
+  <si>
+    <t>Croatian Mixed Doubles Championship</t>
+  </si>
+  <si>
+    <t>Croatian Men Championship, draw 1</t>
+  </si>
+  <si>
+    <t>Croatian Women Championship, draw 1</t>
+  </si>
+  <si>
+    <t>Croatian Men Championship, draw 2</t>
+  </si>
+  <si>
+    <t>Croatian Women Championship, draw 2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1986,13 +2064,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF1A1A1A"/>
-      <name val="Aptos"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FF1A1A1A"/>
       <name val="Aptos"/>
@@ -2131,7 +2202,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2158,9 +2229,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2170,10 +2238,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2194,33 +2259,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -2229,6 +2270,48 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2567,49 +2650,49 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E9B2294-CDE6-49E7-8599-B9647C0F1001}">
   <dimension ref="A1:A10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" style="7"/>
+    <col min="1" max="1" width="8.88671875" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="26" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>621</v>
+        <v>604</v>
       </c>
     </row>
   </sheetData>
@@ -2620,441 +2703,814 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38A2AF21-1D89-4A8A-9C16-4006AA8D9158}">
-  <dimension ref="A1:D36"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H37"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.85546875" style="8" customWidth="1"/>
-    <col min="2" max="2" width="58.85546875" style="8" customWidth="1"/>
-    <col min="3" max="3" width="10.28515625" style="8" customWidth="1"/>
-    <col min="4" max="4" width="45.5703125" style="8" customWidth="1"/>
-    <col min="5" max="16384" width="8.85546875" style="8"/>
+    <col min="1" max="1" width="22.88671875" style="8" customWidth="1"/>
+    <col min="2" max="2" width="5.33203125" style="42" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" style="8" customWidth="1"/>
+    <col min="4" max="4" width="51.44140625" style="8" customWidth="1"/>
+    <col min="5" max="5" width="9.109375" style="8" customWidth="1"/>
+    <col min="6" max="6" width="47.109375" style="8" customWidth="1"/>
+    <col min="7" max="7" width="7.33203125" style="8" customWidth="1"/>
+    <col min="8" max="8" width="45.5546875" style="8" customWidth="1"/>
+    <col min="9" max="9" width="58.109375" style="8" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="15" t="s">
+        <v>562</v>
+      </c>
+      <c r="C1" s="15"/>
+      <c r="E1" s="15"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="12" t="s">
         <v>522</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="12"/>
       <c r="D2" s="9"/>
-    </row>
-    <row r="3" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+      <c r="E2" s="12"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+    </row>
+    <row r="3" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="13" t="s">
         <v>523</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="44"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="10" t="s">
         <v>524</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10" t="s">
+      <c r="E3" s="13"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="12" t="s">
         <v>526</v>
       </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9" t="s">
-        <v>604</v>
-      </c>
+      <c r="B4" s="43"/>
+      <c r="C4" s="12"/>
       <c r="D4" s="9"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="28" t="s">
+      <c r="E4" s="12"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9" t="s">
+        <v>587</v>
+      </c>
+      <c r="H4" s="9"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="36" t="s">
         <v>527</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="45"/>
+      <c r="C5" s="11" t="s">
+        <v>619</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>622</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>637</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>640</v>
+      </c>
+      <c r="G5" s="11">
+        <v>2342</v>
+      </c>
+      <c r="H5" s="34" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="38"/>
+      <c r="B6" s="45"/>
+      <c r="C6" s="11" t="s">
+        <v>619</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>623</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>637</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>641</v>
+      </c>
+      <c r="G6" s="11">
+        <v>2342</v>
+      </c>
+      <c r="H6" s="39"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="37"/>
+      <c r="B7" s="45"/>
+      <c r="C7" s="11" t="s">
+        <v>620</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>623</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>639</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>641</v>
+      </c>
+      <c r="G7" s="11">
+        <v>2341</v>
+      </c>
+      <c r="H7" s="35"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="36" t="s">
+        <v>529</v>
+      </c>
+      <c r="B8" s="45"/>
+      <c r="C8" s="11" t="s">
+        <v>619</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>624</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>637</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>640</v>
+      </c>
+      <c r="G8" s="11"/>
+      <c r="H8" s="34" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="38"/>
+      <c r="B9" s="45"/>
+      <c r="C9" s="11" t="s">
+        <v>619</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>625</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>637</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>641</v>
+      </c>
+      <c r="G9" s="11"/>
+      <c r="H9" s="39"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="37"/>
+      <c r="B10" s="45"/>
+      <c r="C10" s="11" t="s">
+        <v>620</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>626</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>639</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>642</v>
+      </c>
+      <c r="G10" s="11"/>
+      <c r="H10" s="35"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="14" t="s">
+        <v>531</v>
+      </c>
+      <c r="B11" s="45"/>
+      <c r="C11" s="11" t="s">
+        <v>620</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>627</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>639</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>643</v>
+      </c>
+      <c r="G11" s="11"/>
+      <c r="H11" s="10" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="36" t="s">
+        <v>532</v>
+      </c>
+      <c r="B12" s="45"/>
+      <c r="C12" s="11" t="s">
+        <v>620</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>628</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>639</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>644</v>
+      </c>
+      <c r="G12" s="11"/>
+      <c r="H12" s="34" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="38"/>
+      <c r="B13" s="45"/>
+      <c r="C13" s="11" t="s">
+        <v>620</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>629</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>639</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>645</v>
+      </c>
+      <c r="G13" s="11"/>
+      <c r="H13" s="39"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="37"/>
+      <c r="B14" s="45"/>
+      <c r="C14" s="11" t="s">
+        <v>619</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>627</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>637</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>643</v>
+      </c>
+      <c r="G14" s="11"/>
+      <c r="H14" s="35"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="36" t="s">
+        <v>533</v>
+      </c>
+      <c r="B15" s="45"/>
+      <c r="C15" s="11" t="s">
+        <v>620</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>630</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>639</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>646</v>
+      </c>
+      <c r="G15" s="11"/>
+      <c r="H15" s="34" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="38"/>
+      <c r="B16" s="45"/>
+      <c r="C16" s="11" t="s">
+        <v>620</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>631</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>639</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>647</v>
+      </c>
+      <c r="G16" s="11"/>
+      <c r="H16" s="39"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="37"/>
+      <c r="B17" s="45"/>
+      <c r="C17" s="11" t="s">
+        <v>619</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>626</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>637</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>642</v>
+      </c>
+      <c r="G17" s="11"/>
+      <c r="H17" s="35"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="12" t="s">
+        <v>534</v>
+      </c>
+      <c r="B18" s="43"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9" t="s">
+        <v>588</v>
+      </c>
+      <c r="H18" s="9"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="14" t="s">
+        <v>535</v>
+      </c>
+      <c r="B19" s="44" t="s">
+        <v>606</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>620</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>616</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>639</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>536</v>
+      </c>
+      <c r="G19" s="10">
+        <v>841</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" s="32" t="s">
+        <v>540</v>
+      </c>
+      <c r="B20" s="44"/>
+      <c r="C20" s="10" t="s">
+        <v>620</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>614</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>639</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>589</v>
+      </c>
+      <c r="G20" s="10">
+        <v>842</v>
+      </c>
+      <c r="H20" s="34" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" s="33"/>
+      <c r="B21" s="44"/>
+      <c r="C21" s="10" t="s">
+        <v>620</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>615</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>639</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>590</v>
+      </c>
+      <c r="G21" s="10">
+        <v>843</v>
+      </c>
+      <c r="H21" s="35"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" s="25" t="s">
+        <v>542</v>
+      </c>
+      <c r="B22" s="44"/>
+      <c r="C22" s="10" t="s">
+        <v>620</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>617</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>639</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>610</v>
+      </c>
+      <c r="G22" s="10">
+        <v>844</v>
+      </c>
+      <c r="H22" s="25" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" s="25" t="s">
+        <v>544</v>
+      </c>
+      <c r="B23" s="44"/>
+      <c r="C23" s="10" t="s">
+        <v>620</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>618</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>639</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>609</v>
+      </c>
+      <c r="G23" s="10">
+        <v>845</v>
+      </c>
+      <c r="H23" s="25" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" s="36" t="s">
+        <v>546</v>
+      </c>
+      <c r="B24" s="44" t="s">
+        <v>606</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>619</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>617</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>637</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>591</v>
+      </c>
+      <c r="G24" s="10">
+        <v>847</v>
+      </c>
+      <c r="H24" s="34" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" s="37"/>
+      <c r="B25" s="44" t="s">
+        <v>606</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>619</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>618</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>637</v>
+      </c>
+      <c r="F25" s="10" t="s">
         <v>592</v>
       </c>
-      <c r="C5" s="11">
-        <v>2342</v>
-      </c>
-      <c r="D5" s="31" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="29"/>
-      <c r="B6" s="11" t="s">
+      <c r="G25" s="10">
+        <v>848</v>
+      </c>
+      <c r="H25" s="35"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" s="25" t="s">
+        <v>548</v>
+      </c>
+      <c r="B26" s="44"/>
+      <c r="C26" s="10" t="s">
+        <v>620</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>613</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>639</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>549</v>
+      </c>
+      <c r="G26" s="10">
+        <v>852</v>
+      </c>
+      <c r="H26" s="25" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" s="32" t="s">
+        <v>550</v>
+      </c>
+      <c r="B27" s="44"/>
+      <c r="C27" s="10" t="s">
+        <v>619</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>632</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>637</v>
+      </c>
+      <c r="F27" s="10" t="s">
         <v>593</v>
       </c>
-      <c r="C6" s="11">
-        <v>2342</v>
-      </c>
-      <c r="D6" s="32"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="30"/>
-      <c r="B7" s="11" t="s">
+      <c r="G27" s="10">
+        <v>853</v>
+      </c>
+      <c r="H27" s="32" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" s="33"/>
+      <c r="B28" s="44"/>
+      <c r="C28" s="10" t="s">
+        <v>619</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>633</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>637</v>
+      </c>
+      <c r="F28" s="10" t="s">
         <v>594</v>
       </c>
-      <c r="C7" s="11">
-        <v>2341</v>
-      </c>
-      <c r="D7" s="33"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="28" t="s">
-        <v>529</v>
-      </c>
-      <c r="B8" s="11" t="s">
+      <c r="G28" s="10">
+        <v>854</v>
+      </c>
+      <c r="H28" s="33"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" s="25" t="s">
+        <v>551</v>
+      </c>
+      <c r="B29" s="44"/>
+      <c r="C29" s="10" t="s">
+        <v>620</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>633</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>639</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>552</v>
+      </c>
+      <c r="G29" s="10">
+        <v>857</v>
+      </c>
+      <c r="H29" s="10" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" s="25" t="s">
+        <v>553</v>
+      </c>
+      <c r="B30" s="44"/>
+      <c r="C30" s="10" t="s">
+        <v>620</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>632</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>639</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>554</v>
+      </c>
+      <c r="G30" s="10">
+        <v>858</v>
+      </c>
+      <c r="H30" s="10" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="B31" s="44" t="s">
+        <v>606</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>620</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>634</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>639</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>538</v>
+      </c>
+      <c r="G31" s="10"/>
+      <c r="H31" s="10" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" s="14" t="s">
+        <v>556</v>
+      </c>
+      <c r="B32" s="44" t="s">
+        <v>606</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>620</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>616</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>639</v>
+      </c>
+      <c r="F32" s="10" t="s">
+        <v>536</v>
+      </c>
+      <c r="G32" s="10">
+        <v>862</v>
+      </c>
+      <c r="H32" s="10" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" s="40" t="s">
+        <v>558</v>
+      </c>
+      <c r="B33" s="44" t="s">
+        <v>605</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>620</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>635</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>639</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>611</v>
+      </c>
+      <c r="G33" s="10"/>
+      <c r="H33" s="34" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" s="41"/>
+      <c r="B34" s="44" t="s">
+        <v>605</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>620</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>636</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>639</v>
+      </c>
+      <c r="F34" s="10" t="s">
+        <v>612</v>
+      </c>
+      <c r="G34" s="10"/>
+      <c r="H34" s="35"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35" s="36" t="s">
+        <v>559</v>
+      </c>
+      <c r="B35" s="44" t="s">
+        <v>606</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>621</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>632</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>638</v>
+      </c>
+      <c r="F35" s="10" t="s">
         <v>595</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="31" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="29"/>
-      <c r="B9" s="11" t="s">
+      <c r="G35" s="10">
+        <v>859</v>
+      </c>
+      <c r="H35" s="34" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36" s="37"/>
+      <c r="B36" s="44" t="s">
+        <v>606</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>621</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>633</v>
+      </c>
+      <c r="E36" s="10" t="s">
+        <v>638</v>
+      </c>
+      <c r="F36" s="10" t="s">
         <v>596</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="32"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="30"/>
-      <c r="B10" s="11" t="s">
-        <v>597</v>
-      </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="33"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="15" t="s">
-        <v>531</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>532</v>
-      </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="10" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="28" t="s">
-        <v>533</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>598</v>
-      </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="31" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="29"/>
-      <c r="B13" s="11" t="s">
-        <v>599</v>
-      </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="32"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="30"/>
-      <c r="B14" s="11" t="s">
-        <v>600</v>
-      </c>
-      <c r="C14" s="11"/>
-      <c r="D14" s="33"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="28" t="s">
-        <v>534</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>601</v>
-      </c>
-      <c r="C15" s="11"/>
-      <c r="D15" s="31" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="29"/>
-      <c r="B16" s="11" t="s">
-        <v>602</v>
-      </c>
-      <c r="C16" s="11"/>
-      <c r="D16" s="32"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="30"/>
-      <c r="B17" s="11" t="s">
-        <v>603</v>
-      </c>
-      <c r="C17" s="11"/>
-      <c r="D17" s="33"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="13" t="s">
-        <v>535</v>
-      </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9" t="s">
-        <v>605</v>
-      </c>
-      <c r="D18" s="9"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="15" t="s">
-        <v>536</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>537</v>
-      </c>
-      <c r="C19" s="12">
-        <v>841</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="15" t="s">
+      <c r="G36" s="10">
+        <v>860</v>
+      </c>
+      <c r="H36" s="35"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A37" s="14" t="s">
+        <v>560</v>
+      </c>
+      <c r="B37" s="44" t="s">
+        <v>606</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>619</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>613</v>
+      </c>
+      <c r="E37" s="10" t="s">
+        <v>637</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>561</v>
+      </c>
+      <c r="G37" s="10">
+        <v>861</v>
+      </c>
+      <c r="H37" s="10" t="s">
         <v>539</v>
       </c>
-      <c r="B20" s="12" t="s">
-        <v>540</v>
-      </c>
-      <c r="C20" s="12"/>
-      <c r="D20" s="10" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="34" t="s">
-        <v>542</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>606</v>
-      </c>
-      <c r="C21" s="10">
-        <v>842</v>
-      </c>
-      <c r="D21" s="31" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="35"/>
-      <c r="B22" s="10" t="s">
-        <v>607</v>
-      </c>
-      <c r="C22" s="10">
-        <v>843</v>
-      </c>
-      <c r="D22" s="33"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="27" t="s">
-        <v>544</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>545</v>
-      </c>
-      <c r="C23" s="10">
-        <v>844</v>
-      </c>
-      <c r="D23" s="27" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="27" t="s">
-        <v>547</v>
-      </c>
-      <c r="B24" s="10" t="s">
-        <v>548</v>
-      </c>
-      <c r="C24" s="10">
-        <v>845</v>
-      </c>
-      <c r="D24" s="27" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="28" t="s">
-        <v>550</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>608</v>
-      </c>
-      <c r="C25" s="12">
-        <v>847</v>
-      </c>
-      <c r="D25" s="31" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="30"/>
-      <c r="B26" s="12" t="s">
-        <v>609</v>
-      </c>
-      <c r="C26" s="12">
-        <v>848</v>
-      </c>
-      <c r="D26" s="33"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="27" t="s">
-        <v>552</v>
-      </c>
-      <c r="B27" s="10" t="s">
-        <v>553</v>
-      </c>
-      <c r="C27" s="10">
-        <v>852</v>
-      </c>
-      <c r="D27" s="27" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="34" t="s">
-        <v>554</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>610</v>
-      </c>
-      <c r="C28" s="10">
-        <v>853</v>
-      </c>
-      <c r="D28" s="34" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="35"/>
-      <c r="B29" s="10" t="s">
-        <v>611</v>
-      </c>
-      <c r="C29" s="10">
-        <v>854</v>
-      </c>
-      <c r="D29" s="35"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="27" t="s">
-        <v>555</v>
-      </c>
-      <c r="B30" s="10" t="s">
-        <v>556</v>
-      </c>
-      <c r="C30" s="10">
-        <v>857</v>
-      </c>
-      <c r="D30" s="10" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="27" t="s">
-        <v>557</v>
-      </c>
-      <c r="B31" s="10" t="s">
-        <v>558</v>
-      </c>
-      <c r="C31" s="10">
-        <v>858</v>
-      </c>
-      <c r="D31" s="10" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="15" t="s">
-        <v>560</v>
-      </c>
-      <c r="B32" s="12" t="s">
-        <v>537</v>
-      </c>
-      <c r="C32" s="12">
-        <v>862</v>
-      </c>
-      <c r="D32" s="10" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="16" t="s">
-        <v>562</v>
-      </c>
-      <c r="B33" s="12" t="s">
-        <v>563</v>
-      </c>
-      <c r="C33" s="12"/>
-      <c r="D33" s="10" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="28" t="s">
-        <v>564</v>
-      </c>
-      <c r="B34" s="12" t="s">
-        <v>612</v>
-      </c>
-      <c r="C34" s="12">
-        <v>859</v>
-      </c>
-      <c r="D34" s="31" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="30"/>
-      <c r="B35" s="12" t="s">
-        <v>613</v>
-      </c>
-      <c r="C35" s="12">
-        <v>860</v>
-      </c>
-      <c r="D35" s="33"/>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="15" t="s">
-        <v>565</v>
-      </c>
-      <c r="B36" s="12" t="s">
-        <v>566</v>
-      </c>
-      <c r="C36" s="12">
-        <v>861</v>
-      </c>
-      <c r="D36" s="10" t="s">
-        <v>541</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="A34:A35"/>
+  <mergeCells count="18">
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="H5:H7"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="H8:H10"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="H12:H14"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="H27:H28"/>
+    <mergeCell ref="H35:H36"/>
+    <mergeCell ref="A35:A36"/>
     <mergeCell ref="A15:A17"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="D5:D7"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="A12:A14"/>
-    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="H15:H17"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="H33:H34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3063,280 +3519,280 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF19D07F-C891-4FD7-A451-C71533DD2DA9}">
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.140625" customWidth="1"/>
-    <col min="2" max="2" width="14.5703125" customWidth="1"/>
-    <col min="3" max="3" width="31.140625" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" customWidth="1"/>
-    <col min="5" max="5" width="29.5703125" customWidth="1"/>
-    <col min="6" max="6" width="20.7109375" customWidth="1"/>
-    <col min="7" max="7" width="17.140625" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.109375" customWidth="1"/>
+    <col min="2" max="2" width="14.5546875" customWidth="1"/>
+    <col min="3" max="3" width="31.109375" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" customWidth="1"/>
+    <col min="5" max="5" width="29.5546875" customWidth="1"/>
+    <col min="6" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="17.109375" customWidth="1"/>
+    <col min="8" max="8" width="13.109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="20" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="18" t="s">
+        <v>472</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>473</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>474</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>476</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>477</v>
+      </c>
+      <c r="G2" s="18" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="16" t="s">
+        <v>511</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>483</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>512</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>567</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>514</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>513</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="16" t="s">
+        <v>488</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>483</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>489</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>569</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>491</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>490</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="16" t="s">
+        <v>502</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>483</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>503</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>566</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>505</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>504</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="16" t="s">
+        <v>497</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>483</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>498</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>565</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>501</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>500</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="16" t="s">
+        <v>506</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>507</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>508</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>565</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>510</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>509</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="20" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="18" t="s">
+        <v>472</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>473</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>474</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>476</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>575</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>583</v>
+      </c>
+      <c r="G9" s="18" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="16" t="s">
+        <v>515</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>483</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>516</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>570</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>573</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>517</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="16" t="s">
+        <v>492</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>493</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>494</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>567</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>572</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>495</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="16" t="s">
+        <v>519</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>483</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>516</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>569</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>574</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>520</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="16" t="s">
+        <v>482</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>483</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>484</v>
+      </c>
+      <c r="D13" s="17" t="s">
         <v>568</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
-        <v>472</v>
-      </c>
-      <c r="B2" s="20" t="s">
-        <v>473</v>
-      </c>
-      <c r="C2" s="20" t="s">
-        <v>474</v>
-      </c>
-      <c r="D2" s="20" t="s">
-        <v>476</v>
-      </c>
-      <c r="E2" s="20" t="s">
-        <v>479</v>
-      </c>
-      <c r="F2" s="20" t="s">
-        <v>477</v>
-      </c>
-      <c r="G2" s="20" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
-        <v>511</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>483</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>512</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>572</v>
-      </c>
-      <c r="E3" s="18" t="s">
-        <v>514</v>
-      </c>
-      <c r="F3" s="18" t="s">
-        <v>513</v>
-      </c>
-      <c r="G3" s="18" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>488</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>483</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>489</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>574</v>
-      </c>
-      <c r="E4" s="21" t="s">
-        <v>491</v>
-      </c>
-      <c r="F4" s="19" t="s">
-        <v>490</v>
-      </c>
-      <c r="G4" s="18" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
-        <v>502</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>483</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>503</v>
-      </c>
-      <c r="D5" s="19" t="s">
+      <c r="E13" s="17" t="s">
         <v>571</v>
       </c>
-      <c r="E5" s="18" t="s">
-        <v>505</v>
-      </c>
-      <c r="F5" s="18" t="s">
-        <v>504</v>
-      </c>
-      <c r="G5" s="18" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
-        <v>497</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>483</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>498</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>570</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>501</v>
-      </c>
-      <c r="F6" s="18" t="s">
-        <v>500</v>
-      </c>
-      <c r="G6" s="18" t="s">
+      <c r="F13" s="16" t="s">
+        <v>486</v>
+      </c>
+      <c r="G13" s="16" t="s">
         <v>582</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
-        <v>506</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>507</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>508</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>570</v>
-      </c>
-      <c r="E7" s="18" t="s">
-        <v>510</v>
-      </c>
-      <c r="F7" s="18" t="s">
-        <v>509</v>
-      </c>
-      <c r="G7" s="18" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="22" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="20" t="s">
-        <v>472</v>
-      </c>
-      <c r="B9" s="20" t="s">
-        <v>473</v>
-      </c>
-      <c r="C9" s="20" t="s">
-        <v>474</v>
-      </c>
-      <c r="D9" s="20" t="s">
-        <v>476</v>
-      </c>
-      <c r="E9" s="20" t="s">
-        <v>580</v>
-      </c>
-      <c r="F9" s="20" t="s">
-        <v>588</v>
-      </c>
-      <c r="G9" s="20" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="18" t="s">
-        <v>515</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>483</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>516</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>575</v>
-      </c>
-      <c r="E10" s="19" t="s">
-        <v>578</v>
-      </c>
-      <c r="F10" s="18" t="s">
-        <v>517</v>
-      </c>
-      <c r="G10" s="18" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
-        <v>492</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>493</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>494</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>572</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>577</v>
-      </c>
-      <c r="F11" s="18" t="s">
-        <v>495</v>
-      </c>
-      <c r="G11" s="18" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="18" t="s">
-        <v>519</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>483</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>516</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>574</v>
-      </c>
-      <c r="E12" s="19" t="s">
-        <v>579</v>
-      </c>
-      <c r="F12" s="18" t="s">
-        <v>520</v>
-      </c>
-      <c r="G12" s="18" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
-        <v>482</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>483</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>484</v>
-      </c>
-      <c r="D13" s="19" t="s">
-        <v>573</v>
-      </c>
-      <c r="E13" s="19" t="s">
-        <v>576</v>
-      </c>
-      <c r="F13" s="18" t="s">
-        <v>486</v>
-      </c>
-      <c r="G13" s="18" t="s">
-        <v>587</v>
       </c>
     </row>
   </sheetData>
@@ -3347,1237 +3803,1237 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02100B6D-FE78-4CA2-BE15-61CB2638D07F}">
   <dimension ref="A1:D89"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="34.28515625" style="38" customWidth="1"/>
-    <col min="2" max="2" width="49.5703125" style="38" customWidth="1"/>
-    <col min="3" max="3" width="20.5703125" style="38" customWidth="1"/>
-    <col min="4" max="4" width="38.42578125" style="38" customWidth="1"/>
-    <col min="5" max="16384" width="8.85546875" style="38"/>
+    <col min="1" max="1" width="34.33203125" style="28" customWidth="1"/>
+    <col min="2" max="2" width="49.5546875" style="28" customWidth="1"/>
+    <col min="3" max="3" width="20.5546875" style="28" customWidth="1"/>
+    <col min="4" max="4" width="38.44140625" style="28" customWidth="1"/>
+    <col min="5" max="16384" width="8.88671875" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="27" t="s">
         <v>253</v>
       </c>
-      <c r="B1" s="37" t="s">
+      <c r="B1" s="27" t="s">
         <v>254</v>
       </c>
-      <c r="C1" s="37" t="s">
+      <c r="C1" s="27" t="s">
         <v>255</v>
       </c>
-      <c r="D1" s="37" t="s">
+      <c r="D1" s="27" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="39" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="29" t="s">
         <v>83</v>
       </c>
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="29" t="s">
         <v>267</v>
       </c>
-      <c r="C2" s="39" t="s">
+      <c r="C2" s="29" t="s">
         <v>389</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="40" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="30" t="s">
         <v>86</v>
       </c>
-      <c r="B3" s="40" t="s">
+      <c r="B3" s="30" t="s">
         <v>270</v>
       </c>
-      <c r="C3" s="40" t="s">
+      <c r="C3" s="30" t="s">
         <v>389</v>
       </c>
       <c r="D3" s="4"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="40" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="30" t="s">
         <v>278</v>
       </c>
-      <c r="B4" s="40" t="s">
+      <c r="B4" s="30" t="s">
         <v>279</v>
       </c>
-      <c r="C4" s="40" t="s">
+      <c r="C4" s="30" t="s">
         <v>389</v>
       </c>
       <c r="D4" s="4"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="39" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="29" t="s">
         <v>244</v>
       </c>
-      <c r="B5" s="39" t="s">
+      <c r="B5" s="29" t="s">
         <v>281</v>
       </c>
-      <c r="C5" s="39" t="s">
+      <c r="C5" s="29" t="s">
         <v>389</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="39" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="29" t="s">
         <v>245</v>
       </c>
-      <c r="B6" s="39" t="s">
+      <c r="B6" s="29" t="s">
         <v>291</v>
       </c>
-      <c r="C6" s="39" t="s">
+      <c r="C6" s="29" t="s">
         <v>389</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="39" t="s">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="29" t="s">
         <v>243</v>
       </c>
-      <c r="B7" s="39" t="s">
+      <c r="B7" s="29" t="s">
         <v>305</v>
       </c>
-      <c r="C7" s="39" t="s">
+      <c r="C7" s="29" t="s">
         <v>389</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="40" t="s">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="30" t="s">
         <v>344</v>
       </c>
-      <c r="B8" s="40" t="s">
+      <c r="B8" s="30" t="s">
         <v>345</v>
       </c>
-      <c r="C8" s="40" t="s">
+      <c r="C8" s="30" t="s">
         <v>389</v>
       </c>
       <c r="D8" s="4"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="39" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="29" t="s">
         <v>246</v>
       </c>
-      <c r="B9" s="39" t="s">
+      <c r="B9" s="29" t="s">
         <v>347</v>
       </c>
-      <c r="C9" s="39" t="s">
+      <c r="C9" s="29" t="s">
         <v>389</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="40" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="30" t="s">
         <v>260</v>
       </c>
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="30" t="s">
         <v>261</v>
       </c>
-      <c r="C10" s="40" t="s">
+      <c r="C10" s="30" t="s">
         <v>388</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="40" t="s">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="30" t="s">
         <v>228</v>
       </c>
-      <c r="B11" s="40" t="s">
+      <c r="B11" s="30" t="s">
         <v>262</v>
       </c>
-      <c r="C11" s="40" t="s">
+      <c r="C11" s="30" t="s">
         <v>388</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="40" t="s">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="B12" s="40" t="s">
+      <c r="B12" s="30" t="s">
         <v>265</v>
       </c>
-      <c r="C12" s="40" t="s">
+      <c r="C12" s="30" t="s">
         <v>388</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="40" t="s">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="B13" s="40" t="s">
+      <c r="B13" s="30" t="s">
         <v>266</v>
       </c>
-      <c r="C13" s="40" t="s">
+      <c r="C13" s="30" t="s">
         <v>388</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="40" t="s">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="30" t="s">
         <v>229</v>
       </c>
-      <c r="B14" s="40" t="s">
+      <c r="B14" s="30" t="s">
         <v>268</v>
       </c>
-      <c r="C14" s="40" t="s">
+      <c r="C14" s="30" t="s">
         <v>388</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="40" t="s">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="40" t="s">
+      <c r="B15" s="30" t="s">
         <v>273</v>
       </c>
-      <c r="C15" s="40" t="s">
+      <c r="C15" s="30" t="s">
         <v>388</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="40" t="s">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="B16" s="40" t="s">
+      <c r="B16" s="30" t="s">
         <v>282</v>
       </c>
-      <c r="C16" s="40" t="s">
+      <c r="C16" s="30" t="s">
         <v>388</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="40" t="s">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="30" t="s">
         <v>230</v>
       </c>
-      <c r="B17" s="40" t="s">
+      <c r="B17" s="30" t="s">
         <v>283</v>
       </c>
-      <c r="C17" s="40" t="s">
+      <c r="C17" s="30" t="s">
         <v>388</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="40" t="s">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="30" t="s">
         <v>231</v>
       </c>
-      <c r="B18" s="40" t="s">
+      <c r="B18" s="30" t="s">
         <v>287</v>
       </c>
-      <c r="C18" s="40" t="s">
+      <c r="C18" s="30" t="s">
         <v>388</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="40" t="s">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="30" t="s">
         <v>289</v>
       </c>
-      <c r="B19" s="40" t="s">
+      <c r="B19" s="30" t="s">
         <v>290</v>
       </c>
-      <c r="C19" s="40" t="s">
+      <c r="C19" s="30" t="s">
         <v>388</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="40" t="s">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="40" t="s">
+      <c r="B20" s="30" t="s">
         <v>292</v>
       </c>
-      <c r="C20" s="40" t="s">
+      <c r="C20" s="30" t="s">
         <v>388</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="40" t="s">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="40" t="s">
+      <c r="B21" s="30" t="s">
         <v>293</v>
       </c>
-      <c r="C21" s="40" t="s">
+      <c r="C21" s="30" t="s">
         <v>388</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="40" t="s">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="30" t="s">
         <v>232</v>
       </c>
-      <c r="B22" s="40" t="s">
+      <c r="B22" s="30" t="s">
         <v>294</v>
       </c>
-      <c r="C22" s="40" t="s">
+      <c r="C22" s="30" t="s">
         <v>388</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="40" t="s">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="30" t="s">
         <v>233</v>
       </c>
-      <c r="B23" s="40" t="s">
+      <c r="B23" s="30" t="s">
         <v>297</v>
       </c>
-      <c r="C23" s="40" t="s">
+      <c r="C23" s="30" t="s">
         <v>388</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="40" t="s">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="30" t="s">
         <v>298</v>
       </c>
-      <c r="B24" s="40" t="s">
+      <c r="B24" s="30" t="s">
         <v>299</v>
       </c>
-      <c r="C24" s="40" t="s">
+      <c r="C24" s="30" t="s">
         <v>388</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="40" t="s">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="30" t="s">
         <v>116</v>
       </c>
-      <c r="B25" s="40" t="s">
+      <c r="B25" s="30" t="s">
         <v>300</v>
       </c>
-      <c r="C25" s="40" t="s">
+      <c r="C25" s="30" t="s">
         <v>388</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="40" t="s">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="30" t="s">
         <v>306</v>
       </c>
-      <c r="B26" s="40" t="s">
+      <c r="B26" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="C26" s="40" t="s">
+      <c r="C26" s="30" t="s">
         <v>388</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="40" t="s">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="30" t="s">
         <v>310</v>
       </c>
-      <c r="B27" s="40" t="s">
+      <c r="B27" s="30" t="s">
         <v>311</v>
       </c>
-      <c r="C27" s="40" t="s">
+      <c r="C27" s="30" t="s">
         <v>388</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="40" t="s">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="30" t="s">
         <v>235</v>
       </c>
-      <c r="B28" s="40" t="s">
+      <c r="B28" s="30" t="s">
         <v>312</v>
       </c>
-      <c r="C28" s="40" t="s">
+      <c r="C28" s="30" t="s">
         <v>388</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="40" t="s">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="B29" s="40" t="s">
+      <c r="B29" s="30" t="s">
         <v>317</v>
       </c>
-      <c r="C29" s="40" t="s">
+      <c r="C29" s="30" t="s">
         <v>388</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="40" t="s">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="30" t="s">
         <v>236</v>
       </c>
-      <c r="B30" s="40" t="s">
+      <c r="B30" s="30" t="s">
         <v>318</v>
       </c>
-      <c r="C30" s="40" t="s">
+      <c r="C30" s="30" t="s">
         <v>388</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="40" t="s">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="30" t="s">
         <v>319</v>
       </c>
-      <c r="B31" s="40" t="s">
+      <c r="B31" s="30" t="s">
         <v>320</v>
       </c>
-      <c r="C31" s="40" t="s">
+      <c r="C31" s="30" t="s">
         <v>388</v>
       </c>
       <c r="D31" s="4"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="40" t="s">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="40" t="s">
+      <c r="B32" s="30" t="s">
         <v>324</v>
       </c>
-      <c r="C32" s="40" t="s">
+      <c r="C32" s="30" t="s">
         <v>388</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="40" t="s">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="30" t="s">
         <v>237</v>
       </c>
-      <c r="B33" s="40" t="s">
+      <c r="B33" s="30" t="s">
         <v>327</v>
       </c>
-      <c r="C33" s="40" t="s">
+      <c r="C33" s="30" t="s">
         <v>388</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="40" t="s">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="30" t="s">
         <v>333</v>
       </c>
-      <c r="B34" s="40" t="s">
+      <c r="B34" s="30" t="s">
         <v>334</v>
       </c>
-      <c r="C34" s="40" t="s">
+      <c r="C34" s="30" t="s">
         <v>388</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="40" t="s">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="30" t="s">
         <v>238</v>
       </c>
-      <c r="B35" s="40" t="s">
+      <c r="B35" s="30" t="s">
         <v>337</v>
       </c>
-      <c r="C35" s="40" t="s">
+      <c r="C35" s="30" t="s">
         <v>388</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="40" t="s">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="B36" s="40" t="s">
+      <c r="B36" s="30" t="s">
         <v>340</v>
       </c>
-      <c r="C36" s="40" t="s">
+      <c r="C36" s="30" t="s">
         <v>388</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="40" t="s">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" s="30" t="s">
         <v>350</v>
       </c>
-      <c r="B37" s="40" t="s">
+      <c r="B37" s="30" t="s">
         <v>351</v>
       </c>
-      <c r="C37" s="40" t="s">
+      <c r="C37" s="30" t="s">
         <v>388</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="40" t="s">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="B38" s="40" t="s">
+      <c r="B38" s="30" t="s">
         <v>354</v>
       </c>
-      <c r="C38" s="40" t="s">
+      <c r="C38" s="30" t="s">
         <v>388</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="40" t="s">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" s="30" t="s">
         <v>357</v>
       </c>
-      <c r="B39" s="40" t="s">
+      <c r="B39" s="30" t="s">
         <v>358</v>
       </c>
-      <c r="C39" s="40" t="s">
+      <c r="C39" s="30" t="s">
         <v>388</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="40" t="s">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" s="30" t="s">
         <v>363</v>
       </c>
-      <c r="B40" s="40" t="s">
+      <c r="B40" s="30" t="s">
         <v>364</v>
       </c>
-      <c r="C40" s="40" t="s">
+      <c r="C40" s="30" t="s">
         <v>388</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="40" t="s">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" s="30" t="s">
         <v>365</v>
       </c>
-      <c r="B41" s="40" t="s">
+      <c r="B41" s="30" t="s">
         <v>366</v>
       </c>
-      <c r="C41" s="40" t="s">
+      <c r="C41" s="30" t="s">
         <v>388</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="40" t="s">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" s="30" t="s">
         <v>367</v>
       </c>
-      <c r="B42" s="40" t="s">
+      <c r="B42" s="30" t="s">
         <v>368</v>
       </c>
-      <c r="C42" s="40" t="s">
+      <c r="C42" s="30" t="s">
         <v>388</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="40" t="s">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" s="30" t="s">
         <v>240</v>
       </c>
-      <c r="B43" s="40" t="s">
+      <c r="B43" s="30" t="s">
         <v>369</v>
       </c>
-      <c r="C43" s="40" t="s">
+      <c r="C43" s="30" t="s">
         <v>388</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="40" t="s">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" s="30" t="s">
         <v>370</v>
       </c>
-      <c r="B44" s="40" t="s">
+      <c r="B44" s="30" t="s">
         <v>371</v>
       </c>
-      <c r="C44" s="40" t="s">
+      <c r="C44" s="30" t="s">
         <v>388</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="40" t="s">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" s="30" t="s">
         <v>241</v>
       </c>
-      <c r="B45" s="40" t="s">
+      <c r="B45" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="C45" s="40" t="s">
+      <c r="C45" s="30" t="s">
         <v>388</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="40" t="s">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" s="30" t="s">
         <v>376</v>
       </c>
-      <c r="B46" s="40" t="s">
+      <c r="B46" s="30" t="s">
         <v>377</v>
       </c>
-      <c r="C46" s="40" t="s">
+      <c r="C46" s="30" t="s">
         <v>388</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="40" t="s">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" s="30" t="s">
         <v>242</v>
       </c>
-      <c r="B47" s="40" t="s">
+      <c r="B47" s="30" t="s">
         <v>380</v>
       </c>
-      <c r="C47" s="40" t="s">
+      <c r="C47" s="30" t="s">
         <v>388</v>
       </c>
       <c r="D47" s="6" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="40" t="s">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" s="30" t="s">
         <v>381</v>
       </c>
-      <c r="B48" s="40" t="s">
+      <c r="B48" s="30" t="s">
         <v>382</v>
       </c>
-      <c r="C48" s="40" t="s">
+      <c r="C48" s="30" t="s">
         <v>388</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="40" t="s">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" s="30" t="s">
         <v>98</v>
       </c>
-      <c r="B49" s="40" t="s">
+      <c r="B49" s="30" t="s">
         <v>256</v>
       </c>
-      <c r="C49" s="40" t="s">
+      <c r="C49" s="30" t="s">
         <v>257</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="40" t="s">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" s="30" t="s">
         <v>258</v>
       </c>
-      <c r="B50" s="40" t="s">
+      <c r="B50" s="30" t="s">
         <v>259</v>
       </c>
-      <c r="C50" s="40" t="s">
+      <c r="C50" s="30" t="s">
         <v>257</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="40" t="s">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51" s="30" t="s">
         <v>263</v>
       </c>
-      <c r="B51" s="40" t="s">
+      <c r="B51" s="30" t="s">
         <v>264</v>
       </c>
-      <c r="C51" s="40" t="s">
+      <c r="C51" s="30" t="s">
         <v>257</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="40" t="s">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" s="30" t="s">
         <v>100</v>
       </c>
-      <c r="B52" s="40" t="s">
+      <c r="B52" s="30" t="s">
         <v>269</v>
       </c>
-      <c r="C52" s="40" t="s">
+      <c r="C52" s="30" t="s">
         <v>257</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="40" t="s">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53" s="30" t="s">
         <v>271</v>
       </c>
-      <c r="B53" s="40" t="s">
+      <c r="B53" s="30" t="s">
         <v>272</v>
       </c>
-      <c r="C53" s="40" t="s">
+      <c r="C53" s="30" t="s">
         <v>257</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="40" t="s">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54" s="30" t="s">
         <v>274</v>
       </c>
-      <c r="B54" s="40" t="s">
+      <c r="B54" s="30" t="s">
         <v>275</v>
       </c>
-      <c r="C54" s="40" t="s">
+      <c r="C54" s="30" t="s">
         <v>257</v>
       </c>
       <c r="D54" s="6" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="40" t="s">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55" s="30" t="s">
         <v>276</v>
       </c>
-      <c r="B55" s="40" t="s">
+      <c r="B55" s="30" t="s">
         <v>277</v>
       </c>
-      <c r="C55" s="40" t="s">
+      <c r="C55" s="30" t="s">
         <v>257</v>
       </c>
       <c r="D55" s="6" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="40" t="s">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A56" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="B56" s="40" t="s">
+      <c r="B56" s="30" t="s">
         <v>280</v>
       </c>
-      <c r="C56" s="40" t="s">
+      <c r="C56" s="30" t="s">
         <v>257</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="40" t="s">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A57" s="30" t="s">
         <v>217</v>
       </c>
-      <c r="B57" s="41" t="s">
+      <c r="B57" s="31" t="s">
         <v>284</v>
       </c>
-      <c r="C57" s="40" t="s">
+      <c r="C57" s="30" t="s">
         <v>257</v>
       </c>
       <c r="D57" s="6" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="40" t="s">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58" s="30" t="s">
         <v>285</v>
       </c>
-      <c r="B58" s="40" t="s">
+      <c r="B58" s="30" t="s">
         <v>286</v>
       </c>
-      <c r="C58" s="40" t="s">
+      <c r="C58" s="30" t="s">
         <v>257</v>
       </c>
       <c r="D58" s="6" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="40" t="s">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A59" s="30" t="s">
         <v>252</v>
       </c>
-      <c r="B59" s="40" t="s">
+      <c r="B59" s="30" t="s">
         <v>288</v>
       </c>
-      <c r="C59" s="40" t="s">
+      <c r="C59" s="30" t="s">
         <v>257</v>
       </c>
       <c r="D59" s="6" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="40" t="s">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A60" s="30" t="s">
         <v>109</v>
       </c>
-      <c r="B60" s="40" t="s">
+      <c r="B60" s="30" t="s">
         <v>295</v>
       </c>
-      <c r="C60" s="40" t="s">
+      <c r="C60" s="30" t="s">
         <v>257</v>
       </c>
       <c r="D60" s="4"/>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" s="40" t="s">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A61" s="30" t="s">
         <v>112</v>
       </c>
-      <c r="B61" s="40" t="s">
+      <c r="B61" s="30" t="s">
         <v>296</v>
       </c>
-      <c r="C61" s="40" t="s">
+      <c r="C61" s="30" t="s">
         <v>257</v>
       </c>
       <c r="D61" s="6" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="40" t="s">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A62" s="30" t="s">
         <v>301</v>
       </c>
-      <c r="B62" s="40" t="s">
+      <c r="B62" s="30" t="s">
         <v>302</v>
       </c>
-      <c r="C62" s="40" t="s">
+      <c r="C62" s="30" t="s">
         <v>257</v>
       </c>
       <c r="D62" s="4"/>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" s="40" t="s">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A63" s="30" t="s">
         <v>215</v>
       </c>
-      <c r="B63" s="40" t="s">
+      <c r="B63" s="30" t="s">
         <v>303</v>
       </c>
-      <c r="C63" s="40" t="s">
+      <c r="C63" s="30" t="s">
         <v>257</v>
       </c>
       <c r="D63" s="6" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" s="40" t="s">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A64" s="30" t="s">
         <v>247</v>
       </c>
-      <c r="B64" s="40" t="s">
+      <c r="B64" s="30" t="s">
         <v>304</v>
       </c>
-      <c r="C64" s="40" t="s">
+      <c r="C64" s="30" t="s">
         <v>257</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" s="40" t="s">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A65" s="30" t="s">
         <v>308</v>
       </c>
-      <c r="B65" s="40" t="s">
+      <c r="B65" s="30" t="s">
         <v>309</v>
       </c>
-      <c r="C65" s="40" t="s">
+      <c r="C65" s="30" t="s">
         <v>257</v>
       </c>
       <c r="D65" s="4"/>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" s="40" t="s">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A66" s="30" t="s">
         <v>313</v>
       </c>
-      <c r="B66" s="40" t="s">
+      <c r="B66" s="30" t="s">
         <v>314</v>
       </c>
-      <c r="C66" s="40" t="s">
+      <c r="C66" s="30" t="s">
         <v>257</v>
       </c>
       <c r="D66" s="6" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" s="40" t="s">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A67" s="30" t="s">
         <v>315</v>
       </c>
-      <c r="B67" s="40" t="s">
+      <c r="B67" s="30" t="s">
         <v>316</v>
       </c>
-      <c r="C67" s="40" t="s">
+      <c r="C67" s="30" t="s">
         <v>257</v>
       </c>
       <c r="D67" s="6" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" s="40" t="s">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A68" s="30" t="s">
         <v>321</v>
       </c>
-      <c r="B68" s="40" t="s">
+      <c r="B68" s="30" t="s">
         <v>322</v>
       </c>
-      <c r="C68" s="40" t="s">
+      <c r="C68" s="30" t="s">
         <v>257</v>
       </c>
       <c r="D68" s="6" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" s="40" t="s">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A69" s="30" t="s">
         <v>213</v>
       </c>
-      <c r="B69" s="40" t="s">
+      <c r="B69" s="30" t="s">
         <v>323</v>
       </c>
-      <c r="C69" s="40" t="s">
+      <c r="C69" s="30" t="s">
         <v>257</v>
       </c>
       <c r="D69" s="4"/>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" s="40" t="s">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A70" s="30" t="s">
         <v>325</v>
       </c>
-      <c r="B70" s="40" t="s">
+      <c r="B70" s="30" t="s">
         <v>326</v>
       </c>
-      <c r="C70" s="40" t="s">
+      <c r="C70" s="30" t="s">
         <v>257</v>
       </c>
       <c r="D70" s="6" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" s="40" t="s">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A71" s="30" t="s">
         <v>328</v>
       </c>
-      <c r="B71" s="40" t="s">
+      <c r="B71" s="30" t="s">
         <v>329</v>
       </c>
-      <c r="C71" s="40" t="s">
+      <c r="C71" s="30" t="s">
         <v>257</v>
       </c>
       <c r="D71" s="6" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" s="40" t="s">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A72" s="30" t="s">
         <v>126</v>
       </c>
-      <c r="B72" s="40" t="s">
+      <c r="B72" s="30" t="s">
         <v>330</v>
       </c>
-      <c r="C72" s="40" t="s">
+      <c r="C72" s="30" t="s">
         <v>257</v>
       </c>
       <c r="D72" s="6" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" s="40" t="s">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A73" s="30" t="s">
         <v>331</v>
       </c>
-      <c r="B73" s="40" t="s">
+      <c r="B73" s="30" t="s">
         <v>332</v>
       </c>
-      <c r="C73" s="40" t="s">
+      <c r="C73" s="30" t="s">
         <v>257</v>
       </c>
       <c r="D73" s="6" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" s="40" t="s">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A74" s="30" t="s">
         <v>335</v>
       </c>
-      <c r="B74" s="40" t="s">
+      <c r="B74" s="30" t="s">
         <v>336</v>
       </c>
-      <c r="C74" s="40" t="s">
+      <c r="C74" s="30" t="s">
         <v>257</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" s="40" t="s">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A75" s="30" t="s">
         <v>338</v>
       </c>
-      <c r="B75" s="40" t="s">
+      <c r="B75" s="30" t="s">
         <v>339</v>
       </c>
-      <c r="C75" s="40" t="s">
+      <c r="C75" s="30" t="s">
         <v>257</v>
       </c>
       <c r="D75" s="6" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" s="40" t="s">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A76" s="30" t="s">
         <v>248</v>
       </c>
-      <c r="B76" s="40" t="s">
+      <c r="B76" s="30" t="s">
         <v>341</v>
       </c>
-      <c r="C76" s="40" t="s">
+      <c r="C76" s="30" t="s">
         <v>257</v>
       </c>
       <c r="D76" s="6" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A77" s="40" t="s">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A77" s="30" t="s">
         <v>342</v>
       </c>
-      <c r="B77" s="40" t="s">
+      <c r="B77" s="30" t="s">
         <v>343</v>
       </c>
-      <c r="C77" s="40" t="s">
+      <c r="C77" s="30" t="s">
         <v>257</v>
       </c>
       <c r="D77" s="4"/>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" s="40" t="s">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A78" s="30" t="s">
         <v>249</v>
       </c>
-      <c r="B78" s="40" t="s">
+      <c r="B78" s="30" t="s">
         <v>346</v>
       </c>
-      <c r="C78" s="40" t="s">
+      <c r="C78" s="30" t="s">
         <v>257</v>
       </c>
       <c r="D78" s="6" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79" s="40" t="s">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A79" s="30" t="s">
         <v>348</v>
       </c>
-      <c r="B79" s="40" t="s">
+      <c r="B79" s="30" t="s">
         <v>349</v>
       </c>
-      <c r="C79" s="40" t="s">
+      <c r="C79" s="30" t="s">
         <v>257</v>
       </c>
       <c r="D79" s="6" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" s="40" t="s">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A80" s="30" t="s">
         <v>352</v>
       </c>
-      <c r="B80" s="40" t="s">
+      <c r="B80" s="30" t="s">
         <v>353</v>
       </c>
-      <c r="C80" s="40" t="s">
+      <c r="C80" s="30" t="s">
         <v>257</v>
       </c>
       <c r="D80" s="6" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A81" s="40" t="s">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A81" s="30" t="s">
         <v>355</v>
       </c>
-      <c r="B81" s="40" t="s">
+      <c r="B81" s="30" t="s">
         <v>356</v>
       </c>
-      <c r="C81" s="40" t="s">
+      <c r="C81" s="30" t="s">
         <v>257</v>
       </c>
       <c r="D81" s="6" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" s="40" t="s">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A82" s="30" t="s">
         <v>359</v>
       </c>
-      <c r="B82" s="40" t="s">
+      <c r="B82" s="30" t="s">
         <v>360</v>
       </c>
-      <c r="C82" s="40" t="s">
+      <c r="C82" s="30" t="s">
         <v>257</v>
       </c>
       <c r="D82" s="6" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A83" s="40" t="s">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A83" s="30" t="s">
         <v>361</v>
       </c>
-      <c r="B83" s="40" t="s">
+      <c r="B83" s="30" t="s">
         <v>362</v>
       </c>
-      <c r="C83" s="40" t="s">
+      <c r="C83" s="30" t="s">
         <v>257</v>
       </c>
       <c r="D83" s="6" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A84" s="40" t="s">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A84" s="30" t="s">
         <v>251</v>
       </c>
-      <c r="B84" s="40" t="s">
+      <c r="B84" s="30" t="s">
         <v>372</v>
       </c>
-      <c r="C84" s="40" t="s">
+      <c r="C84" s="30" t="s">
         <v>257</v>
       </c>
       <c r="D84" s="6" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A85" s="40" t="s">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A85" s="30" t="s">
         <v>374</v>
       </c>
-      <c r="B85" s="41" t="s">
+      <c r="B85" s="31" t="s">
         <v>375</v>
       </c>
-      <c r="C85" s="40" t="s">
+      <c r="C85" s="30" t="s">
         <v>257</v>
       </c>
       <c r="D85" s="6" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A86" s="40" t="s">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A86" s="30" t="s">
         <v>378</v>
       </c>
-      <c r="B86" s="40" t="s">
+      <c r="B86" s="30" t="s">
         <v>379</v>
       </c>
-      <c r="C86" s="40" t="s">
+      <c r="C86" s="30" t="s">
         <v>257</v>
       </c>
       <c r="D86" s="6" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A87" s="40" t="s">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A87" s="30" t="s">
         <v>383</v>
       </c>
-      <c r="B87" s="40" t="s">
+      <c r="B87" s="30" t="s">
         <v>384</v>
       </c>
-      <c r="C87" s="40" t="s">
+      <c r="C87" s="30" t="s">
         <v>257</v>
       </c>
       <c r="D87" s="6" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A88" s="40" t="s">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A88" s="30" t="s">
         <v>385</v>
       </c>
-      <c r="B88" s="40" t="s">
+      <c r="B88" s="30" t="s">
         <v>386</v>
       </c>
-      <c r="C88" s="40" t="s">
+      <c r="C88" s="30" t="s">
         <v>257</v>
       </c>
       <c r="D88" s="6" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A89" s="40" t="s">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A89" s="30" t="s">
         <v>250</v>
       </c>
-      <c r="B89" s="40" t="s">
+      <c r="B89" s="30" t="s">
         <v>387</v>
       </c>
-      <c r="C89" s="40" t="s">
+      <c r="C89" s="30" t="s">
         <v>257</v>
       </c>
       <c r="D89" s="6" t="s">
@@ -4677,17 +5133,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D2DE0FD-72B8-47D0-8668-3E63A2804089}">
   <dimension ref="A1:B155"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="35.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="35.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>226</v>
       </c>
@@ -4695,7 +5151,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -4703,7 +5159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
@@ -4711,7 +5167,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
@@ -4719,7 +5175,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -4727,7 +5183,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -4735,7 +5191,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
@@ -4743,7 +5199,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
@@ -4751,7 +5207,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
@@ -4759,7 +5215,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
@@ -4767,7 +5223,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>15</v>
       </c>
@@ -4775,7 +5231,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
@@ -4783,7 +5239,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
@@ -4791,7 +5247,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>21</v>
       </c>
@@ -4799,7 +5255,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>23</v>
       </c>
@@ -4807,7 +5263,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>25</v>
       </c>
@@ -4815,7 +5271,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>27</v>
       </c>
@@ -4823,7 +5279,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>29</v>
       </c>
@@ -4831,7 +5287,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>31</v>
       </c>
@@ -4839,7 +5295,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>32</v>
       </c>
@@ -4847,7 +5303,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>33</v>
       </c>
@@ -4855,7 +5311,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>35</v>
       </c>
@@ -4863,7 +5319,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>36</v>
       </c>
@@ -4871,7 +5327,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>37</v>
       </c>
@@ -4879,7 +5335,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>39</v>
       </c>
@@ -4887,7 +5343,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>40</v>
       </c>
@@ -4895,7 +5351,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>42</v>
       </c>
@@ -4903,7 +5359,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>44</v>
       </c>
@@ -4911,7 +5367,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>46</v>
       </c>
@@ -4919,7 +5375,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>47</v>
       </c>
@@ -4927,7 +5383,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>48</v>
       </c>
@@ -4935,7 +5391,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>49</v>
       </c>
@@ -4943,7 +5399,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>50</v>
       </c>
@@ -4951,7 +5407,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>51</v>
       </c>
@@ -4959,7 +5415,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>53</v>
       </c>
@@ -4967,7 +5423,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>55</v>
       </c>
@@ -4975,7 +5431,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>56</v>
       </c>
@@ -4983,7 +5439,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>57</v>
       </c>
@@ -4991,7 +5447,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>59</v>
       </c>
@@ -4999,7 +5455,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>60</v>
       </c>
@@ -5007,7 +5463,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>61</v>
       </c>
@@ -5015,7 +5471,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>62</v>
       </c>
@@ -5023,7 +5479,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>64</v>
       </c>
@@ -5031,7 +5487,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>65</v>
       </c>
@@ -5039,7 +5495,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>67</v>
       </c>
@@ -5047,7 +5503,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>68</v>
       </c>
@@ -5055,7 +5511,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>69</v>
       </c>
@@ -5063,7 +5519,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>71</v>
       </c>
@@ -5071,7 +5527,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>73</v>
       </c>
@@ -5079,7 +5535,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>75</v>
       </c>
@@ -5087,7 +5543,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>76</v>
       </c>
@@ -5095,7 +5551,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>78</v>
       </c>
@@ -5103,7 +5559,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>79</v>
       </c>
@@ -5111,7 +5567,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>81</v>
       </c>
@@ -5119,7 +5575,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>83</v>
       </c>
@@ -5127,7 +5583,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>85</v>
       </c>
@@ -5135,7 +5591,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>86</v>
       </c>
@@ -5143,7 +5599,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>88</v>
       </c>
@@ -5151,7 +5607,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>89</v>
       </c>
@@ -5159,7 +5615,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>90</v>
       </c>
@@ -5167,7 +5623,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>91</v>
       </c>
@@ -5175,7 +5631,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>86</v>
       </c>
@@ -5183,7 +5639,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>92</v>
       </c>
@@ -5191,7 +5647,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>92</v>
       </c>
@@ -5199,7 +5655,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>95</v>
       </c>
@@ -5207,7 +5663,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>97</v>
       </c>
@@ -5215,7 +5671,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>98</v>
       </c>
@@ -5223,7 +5679,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>100</v>
       </c>
@@ -5231,7 +5687,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>102</v>
       </c>
@@ -5239,7 +5695,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>103</v>
       </c>
@@ -5247,7 +5703,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>104</v>
       </c>
@@ -5255,7 +5711,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>106</v>
       </c>
@@ -5263,7 +5719,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>107</v>
       </c>
@@ -5271,7 +5727,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>109</v>
       </c>
@@ -5279,7 +5735,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>111</v>
       </c>
@@ -5287,7 +5743,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>112</v>
       </c>
@@ -5295,7 +5751,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>114</v>
       </c>
@@ -5303,7 +5759,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>116</v>
       </c>
@@ -5311,7 +5767,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>118</v>
       </c>
@@ -5319,7 +5775,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>119</v>
       </c>
@@ -5327,7 +5783,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>120</v>
       </c>
@@ -5335,7 +5791,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>121</v>
       </c>
@@ -5343,7 +5799,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>123</v>
       </c>
@@ -5351,7 +5807,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>125</v>
       </c>
@@ -5359,7 +5815,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
         <v>126</v>
       </c>
@@ -5367,7 +5823,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>128</v>
       </c>
@@ -5375,7 +5831,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>129</v>
       </c>
@@ -5383,7 +5839,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>130</v>
       </c>
@@ -5391,7 +5847,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>131</v>
       </c>
@@ -5399,7 +5855,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>132</v>
       </c>
@@ -5407,7 +5863,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
         <v>133</v>
       </c>
@@ -5415,7 +5871,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
         <v>134</v>
       </c>
@@ -5423,7 +5879,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
         <v>135</v>
       </c>
@@ -5431,7 +5887,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
         <v>137</v>
       </c>
@@ -5439,7 +5895,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
         <v>138</v>
       </c>
@@ -5447,7 +5903,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
         <v>139</v>
       </c>
@@ -5455,7 +5911,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
         <v>140</v>
       </c>
@@ -5463,7 +5919,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
         <v>141</v>
       </c>
@@ -5471,7 +5927,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
         <v>142</v>
       </c>
@@ -5479,7 +5935,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
         <v>143</v>
       </c>
@@ -5487,7 +5943,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>144</v>
       </c>
@@ -5495,7 +5951,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
         <v>145</v>
       </c>
@@ -5503,7 +5959,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
         <v>147</v>
       </c>
@@ -5511,7 +5967,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
         <v>148</v>
       </c>
@@ -5519,7 +5975,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
         <v>149</v>
       </c>
@@ -5527,7 +5983,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
         <v>150</v>
       </c>
@@ -5535,7 +5991,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
         <v>152</v>
       </c>
@@ -5543,7 +5999,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
         <v>153</v>
       </c>
@@ -5551,7 +6007,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
         <v>154</v>
       </c>
@@ -5559,7 +6015,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
         <v>156</v>
       </c>
@@ -5567,7 +6023,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
         <v>157</v>
       </c>
@@ -5575,7 +6031,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
         <v>159</v>
       </c>
@@ -5583,7 +6039,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
         <v>161</v>
       </c>
@@ -5591,7 +6047,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
         <v>163</v>
       </c>
@@ -5599,7 +6055,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
         <v>165</v>
       </c>
@@ -5607,7 +6063,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
         <v>167</v>
       </c>
@@ -5615,7 +6071,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
         <v>169</v>
       </c>
@@ -5623,7 +6079,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
         <v>170</v>
       </c>
@@ -5631,7 +6087,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
         <v>171</v>
       </c>
@@ -5639,7 +6095,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
         <v>172</v>
       </c>
@@ -5647,7 +6103,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
         <v>173</v>
       </c>
@@ -5655,7 +6111,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
         <v>174</v>
       </c>
@@ -5663,7 +6119,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
         <v>176</v>
       </c>
@@ -5671,7 +6127,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
         <v>177</v>
       </c>
@@ -5679,7 +6135,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
         <v>178</v>
       </c>
@@ -5687,7 +6143,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
         <v>179</v>
       </c>
@@ -5695,7 +6151,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
         <v>181</v>
       </c>
@@ -5703,7 +6159,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
         <v>182</v>
       </c>
@@ -5711,7 +6167,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
         <v>183</v>
       </c>
@@ -5719,7 +6175,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
         <v>183</v>
       </c>
@@ -5727,7 +6183,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
         <v>186</v>
       </c>
@@ -5735,7 +6191,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
         <v>188</v>
       </c>
@@ -5743,7 +6199,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
         <v>190</v>
       </c>
@@ -5751,7 +6207,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
         <v>191</v>
       </c>
@@ -5759,7 +6215,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
         <v>193</v>
       </c>
@@ -5767,7 +6223,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
         <v>195</v>
       </c>
@@ -5775,7 +6231,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
         <v>197</v>
       </c>
@@ -5783,7 +6239,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
         <v>199</v>
       </c>
@@ -5791,7 +6247,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
         <v>201</v>
       </c>
@@ -5799,7 +6255,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
         <v>100</v>
       </c>
@@ -5807,7 +6263,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
         <v>204</v>
       </c>
@@ -5815,7 +6271,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
         <v>206</v>
       </c>
@@ -5823,7 +6279,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
         <v>208</v>
       </c>
@@ -5831,7 +6287,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
         <v>210</v>
       </c>
@@ -5839,7 +6295,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
         <v>211</v>
       </c>
@@ -5847,7 +6303,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
         <v>212</v>
       </c>
@@ -5855,7 +6311,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
         <v>213</v>
       </c>
@@ -5863,7 +6319,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
         <v>215</v>
       </c>
@@ -5871,7 +6327,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
         <v>217</v>
       </c>
@@ -5879,7 +6335,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
         <v>219</v>
       </c>
@@ -5887,7 +6343,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
         <v>220</v>
       </c>
@@ -5895,7 +6351,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
         <v>222</v>
       </c>
@@ -5903,7 +6359,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
         <v>224</v>
       </c>
@@ -5920,377 +6376,377 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E488C0EA-2C28-4978-995C-65490886A988}">
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="23" customWidth="1"/>
-    <col min="5" max="6" width="11.28515625" customWidth="1"/>
+    <col min="1" max="1" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.44140625" style="21" customWidth="1"/>
+    <col min="5" max="6" width="11.33203125" customWidth="1"/>
     <col min="7" max="7" width="16" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.6640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="20" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="18" t="s">
         <v>472</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="18" t="s">
         <v>473</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="18" t="s">
         <v>474</v>
       </c>
-      <c r="D2" s="24" t="s">
-        <v>590</v>
-      </c>
-      <c r="E2" s="20" t="s">
+      <c r="D2" s="22" t="s">
+        <v>585</v>
+      </c>
+      <c r="E2" s="18" t="s">
         <v>475</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="18" t="s">
         <v>476</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="G2" s="18" t="s">
         <v>477</v>
       </c>
-      <c r="H2" s="20" t="s">
+      <c r="H2" s="18" t="s">
         <v>478</v>
       </c>
-      <c r="I2" s="20" t="s">
+      <c r="I2" s="18" t="s">
         <v>479</v>
       </c>
-      <c r="J2" s="20" t="s">
+      <c r="J2" s="18" t="s">
         <v>480</v>
       </c>
-      <c r="K2" s="20" t="s">
+      <c r="K2" s="18" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="16" t="s">
         <v>497</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="16" t="s">
         <v>483</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="16" t="s">
         <v>498</v>
       </c>
-      <c r="D3" s="25">
+      <c r="D3" s="23">
         <v>29853315204</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="16" t="s">
         <v>499</v>
       </c>
-      <c r="F3" s="19">
+      <c r="F3" s="17">
         <v>43320</v>
       </c>
-      <c r="G3" s="18" t="s">
+      <c r="G3" s="16" t="s">
         <v>500</v>
       </c>
-      <c r="H3" s="19">
+      <c r="H3" s="17">
         <v>46345</v>
       </c>
-      <c r="I3" s="18" t="s">
+      <c r="I3" s="16" t="s">
         <v>501</v>
       </c>
-      <c r="J3" s="18"/>
-      <c r="K3" s="18"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
+      <c r="J3" s="16"/>
+      <c r="K3" s="16"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="16" t="s">
         <v>502</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="16" t="s">
         <v>483</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="16" t="s">
         <v>503</v>
       </c>
-      <c r="D4" s="25">
+      <c r="D4" s="23">
         <v>23060715807</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="16" t="s">
         <v>499</v>
       </c>
-      <c r="F4" s="19">
+      <c r="F4" s="17">
         <v>40239</v>
       </c>
-      <c r="G4" s="18" t="s">
+      <c r="G4" s="16" t="s">
         <v>504</v>
       </c>
-      <c r="H4" s="19">
+      <c r="H4" s="17">
         <v>46397</v>
       </c>
-      <c r="I4" s="18" t="s">
+      <c r="I4" s="16" t="s">
         <v>505</v>
       </c>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
+      <c r="J4" s="16"/>
+      <c r="K4" s="16"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="16" t="s">
         <v>506</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="16" t="s">
         <v>507</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="16" t="s">
         <v>508</v>
       </c>
-      <c r="D5" s="26" t="s">
-        <v>591</v>
-      </c>
-      <c r="E5" s="18" t="s">
+      <c r="D5" s="24" t="s">
+        <v>586</v>
+      </c>
+      <c r="E5" s="16" t="s">
         <v>499</v>
       </c>
-      <c r="F5" s="19">
+      <c r="F5" s="17">
         <v>43343</v>
       </c>
-      <c r="G5" s="18" t="s">
+      <c r="G5" s="16" t="s">
         <v>509</v>
       </c>
-      <c r="H5" s="19">
+      <c r="H5" s="17">
         <v>46384</v>
       </c>
-      <c r="I5" s="18" t="s">
+      <c r="I5" s="16" t="s">
         <v>510</v>
       </c>
-      <c r="J5" s="18"/>
-      <c r="K5" s="18"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
+      <c r="J5" s="16"/>
+      <c r="K5" s="16"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="16" t="s">
         <v>511</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="16" t="s">
         <v>483</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="16" t="s">
         <v>512</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="23">
         <v>49289106763</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="16" t="s">
         <v>499</v>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="17">
         <v>37681</v>
       </c>
-      <c r="G6" s="18" t="s">
+      <c r="G6" s="16" t="s">
         <v>513</v>
       </c>
-      <c r="H6" s="19">
+      <c r="H6" s="17">
         <v>46447</v>
       </c>
-      <c r="I6" s="18" t="s">
+      <c r="I6" s="16" t="s">
         <v>514</v>
       </c>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="22" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="20" t="s">
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="20" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="18" t="s">
         <v>472</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="18" t="s">
         <v>473</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="18" t="s">
         <v>474</v>
       </c>
-      <c r="D8" s="24" t="s">
-        <v>590</v>
-      </c>
-      <c r="E8" s="20" t="s">
+      <c r="D8" s="22" t="s">
+        <v>585</v>
+      </c>
+      <c r="E8" s="18" t="s">
         <v>475</v>
       </c>
-      <c r="F8" s="20" t="s">
+      <c r="F8" s="18" t="s">
         <v>476</v>
       </c>
-      <c r="G8" s="20" t="s">
+      <c r="G8" s="18" t="s">
         <v>477</v>
       </c>
-      <c r="H8" s="20" t="s">
+      <c r="H8" s="18" t="s">
         <v>478</v>
       </c>
-      <c r="I8" s="20" t="s">
+      <c r="I8" s="18" t="s">
         <v>479</v>
       </c>
-      <c r="J8" s="20" t="s">
+      <c r="J8" s="18" t="s">
         <v>480</v>
       </c>
-      <c r="K8" s="20" t="s">
+      <c r="K8" s="18" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="18" t="s">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="16" t="s">
         <v>482</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="16" t="s">
         <v>483</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="16" t="s">
         <v>484</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="23">
         <v>29216894945</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="16" t="s">
         <v>485</v>
       </c>
-      <c r="F9" s="19">
+      <c r="F9" s="17">
         <v>39144</v>
       </c>
-      <c r="G9" s="18" t="s">
+      <c r="G9" s="16" t="s">
         <v>486</v>
       </c>
-      <c r="H9" s="19">
+      <c r="H9" s="17">
         <v>44087</v>
       </c>
-      <c r="I9" s="18" t="s">
+      <c r="I9" s="16" t="s">
         <v>487</v>
       </c>
-      <c r="J9" s="18"/>
-      <c r="K9" s="18"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="18" t="s">
+      <c r="J9" s="16"/>
+      <c r="K9" s="16"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="16" t="s">
         <v>488</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="16" t="s">
         <v>483</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="16" t="s">
         <v>489</v>
       </c>
-      <c r="D10" s="25">
+      <c r="D10" s="23">
         <v>62904723481</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="16" t="s">
         <v>485</v>
       </c>
-      <c r="F10" s="19">
+      <c r="F10" s="17">
         <v>38260</v>
       </c>
-      <c r="G10" s="18" t="s">
+      <c r="G10" s="16" t="s">
         <v>490</v>
       </c>
-      <c r="H10" s="19">
+      <c r="H10" s="17">
         <v>47274</v>
       </c>
-      <c r="I10" s="18" t="s">
+      <c r="I10" s="16" t="s">
         <v>491</v>
       </c>
-      <c r="J10" s="18"/>
-      <c r="K10" s="18"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
+      <c r="J10" s="16"/>
+      <c r="K10" s="16"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="16" t="s">
         <v>492</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="16" t="s">
         <v>493</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="16" t="s">
         <v>494</v>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="23">
         <v>16553574646</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="16" t="s">
         <v>485</v>
       </c>
-      <c r="F11" s="19">
+      <c r="F11" s="17">
         <v>37731</v>
       </c>
-      <c r="G11" s="18" t="s">
+      <c r="G11" s="16" t="s">
         <v>495</v>
       </c>
-      <c r="H11" s="19">
+      <c r="H11" s="17">
         <v>41946</v>
       </c>
-      <c r="I11" s="18" t="s">
+      <c r="I11" s="16" t="s">
         <v>496</v>
       </c>
-      <c r="J11" s="18"/>
-      <c r="K11" s="18"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="18" t="s">
+      <c r="J11" s="16"/>
+      <c r="K11" s="16"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="16" t="s">
         <v>515</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="16" t="s">
         <v>483</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="16" t="s">
         <v>516</v>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="23">
         <v>39039799048</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="16" t="s">
         <v>485</v>
       </c>
-      <c r="F12" s="19">
+      <c r="F12" s="17">
         <v>37605</v>
       </c>
-      <c r="G12" s="18" t="s">
+      <c r="G12" s="16" t="s">
         <v>517</v>
       </c>
-      <c r="H12" s="19">
+      <c r="H12" s="17">
         <v>45571</v>
       </c>
-      <c r="I12" s="18" t="s">
+      <c r="I12" s="16" t="s">
         <v>518</v>
       </c>
-      <c r="J12" s="18"/>
-      <c r="K12" s="18"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
+      <c r="J12" s="16"/>
+      <c r="K12" s="16"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="16" t="s">
         <v>519</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="16" t="s">
         <v>483</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="16" t="s">
         <v>516</v>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="23">
         <v>25782512086</v>
       </c>
-      <c r="E13" s="18" t="s">
+      <c r="E13" s="16" t="s">
         <v>485</v>
       </c>
-      <c r="F13" s="19">
+      <c r="F13" s="17">
         <v>38080</v>
       </c>
-      <c r="G13" s="18" t="s">
+      <c r="G13" s="16" t="s">
         <v>520</v>
       </c>
-      <c r="H13" s="19">
+      <c r="H13" s="17">
         <v>42643</v>
       </c>
-      <c r="I13" s="18" t="s">
+      <c r="I13" s="16" t="s">
         <v>521</v>
       </c>
-      <c r="J13" s="18"/>
-      <c r="K13" s="18"/>
+      <c r="J13" s="16"/>
+      <c r="K13" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/podaci/hcs-web-data.xlsx
+++ b/podaci/hcs-web-data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30522"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projekti\curling-hr\podaci\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A25EA87-180C-4FFA-9E44-E25AC262C195}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1759ABC1-E865-4A24-9A52-70D879FE69BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="28296" windowHeight="15456" activeTab="1" xr2:uid="{63D9C5CB-4420-4CCB-9E09-733AC492CE83}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{63D9C5CB-4420-4CCB-9E09-733AC492CE83}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="2" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="648">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="676">
   <si>
     <t>Ivan Veštić</t>
   </si>
@@ -1664,9 +1664,6 @@
     <t>World Mixed Curling Championship</t>
   </si>
   <si>
-    <t>?</t>
-  </si>
-  <si>
     <t>27.10. – 01.11.2026.</t>
   </si>
   <si>
@@ -1989,6 +1986,93 @@
   </si>
   <si>
     <t>Croatian Women Championship, draw 2</t>
+  </si>
+  <si>
+    <t>Kategorija</t>
+  </si>
+  <si>
+    <t>Disciplina</t>
+  </si>
+  <si>
+    <t>Natjecanje</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Competition</t>
+  </si>
+  <si>
+    <t>Discipline</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>Ž</t>
+  </si>
+  <si>
+    <t>MC</t>
+  </si>
+  <si>
+    <t>MP</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>MIX</t>
+  </si>
+  <si>
+    <t>MD</t>
+  </si>
+  <si>
+    <t>Link</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>Zagreb Fair</t>
+  </si>
+  <si>
+    <t>Lokacija</t>
+  </si>
+  <si>
+    <t>Budimpešta, Hungary</t>
+  </si>
+  <si>
+    <t>Brunico, Italy</t>
+  </si>
+  <si>
+    <t>Lafayette, USA</t>
+  </si>
+  <si>
+    <t>Ostrava, Czechia</t>
+  </si>
+  <si>
+    <t>Aberdeen, Scotland</t>
+  </si>
+  <si>
+    <t>Östersund, Sweden</t>
+  </si>
+  <si>
+    <t>Lohja, Finland</t>
+  </si>
+  <si>
+    <t>Saint John, Canada</t>
+  </si>
+  <si>
+    <t>Penticton, Canada</t>
+  </si>
+  <si>
+    <t>Winnipeg, Canada</t>
+  </si>
+  <si>
+    <t>BNO</t>
+  </si>
+  <si>
+    <t>TBA</t>
   </si>
 </sst>
 </file>
@@ -2271,36 +2355,6 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2312,6 +2366,36 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2650,49 +2734,49 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E9B2294-CDE6-49E7-8599-B9647C0F1001}">
   <dimension ref="A1:A10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="7"/>
+    <col min="1" max="1" width="8.85546875" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
         <v>602</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
         <v>603</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
-        <v>604</v>
       </c>
     </row>
   </sheetData>
@@ -2703,814 +2787,1127 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38A2AF21-1D89-4A8A-9C16-4006AA8D9158}">
-  <dimension ref="A1:H37"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K37"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.88671875" style="8" customWidth="1"/>
-    <col min="2" max="2" width="5.33203125" style="42" customWidth="1"/>
-    <col min="3" max="3" width="9.109375" style="8" customWidth="1"/>
-    <col min="4" max="4" width="51.44140625" style="8" customWidth="1"/>
-    <col min="5" max="5" width="9.109375" style="8" customWidth="1"/>
-    <col min="6" max="6" width="47.109375" style="8" customWidth="1"/>
-    <col min="7" max="7" width="7.33203125" style="8" customWidth="1"/>
-    <col min="8" max="8" width="45.5546875" style="8" customWidth="1"/>
-    <col min="9" max="9" width="58.109375" style="8" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="8"/>
+    <col min="1" max="1" width="22.85546875" style="8" customWidth="1"/>
+    <col min="2" max="2" width="5.28515625" style="32" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="51.42578125" style="8" customWidth="1"/>
+    <col min="6" max="6" width="22.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="47.140625" style="8" customWidth="1"/>
+    <col min="10" max="10" width="21.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="53" style="8" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="58.140625" style="8" customWidth="1"/>
+    <col min="13" max="16384" width="8.85546875" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>562</v>
-      </c>
-      <c r="C1" s="15"/>
-      <c r="E1" s="15"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+        <v>561</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>647</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>648</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>649</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>663</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>650</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>652</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>651</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>661</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>522</v>
       </c>
-      <c r="B2" s="43"/>
+      <c r="B2" s="33"/>
       <c r="C2" s="12"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="9"/>
       <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-    </row>
-    <row r="3" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+    </row>
+    <row r="3" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>523</v>
       </c>
-      <c r="B3" s="44"/>
+      <c r="B3" s="34"/>
       <c r="C3" s="13"/>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="13"/>
+      <c r="E3" s="10" t="s">
         <v>524</v>
       </c>
-      <c r="E3" s="13"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10" t="s">
+      <c r="F3" s="10" t="s">
         <v>525</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10" t="s">
+        <v>662</v>
+      </c>
+      <c r="K3" s="10"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
         <v>526</v>
       </c>
-      <c r="B4" s="43"/>
+      <c r="B4" s="33"/>
       <c r="C4" s="12"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="9"/>
       <c r="F4" s="9"/>
-      <c r="G4" s="9" t="s">
-        <v>587</v>
-      </c>
-      <c r="H4" s="9"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="36" t="s">
         <v>527</v>
       </c>
-      <c r="B5" s="45"/>
+      <c r="B5" s="35"/>
       <c r="C5" s="11" t="s">
+        <v>618</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>653</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>621</v>
+      </c>
+      <c r="F5" s="39" t="s">
+        <v>528</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>636</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>653</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>639</v>
+      </c>
+      <c r="J5" s="39" t="s">
+        <v>664</v>
+      </c>
+      <c r="K5" s="11">
+        <v>2342</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="37"/>
+      <c r="B6" s="35"/>
+      <c r="C6" s="11" t="s">
+        <v>618</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>654</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>622</v>
+      </c>
+      <c r="F6" s="40"/>
+      <c r="G6" s="11" t="s">
+        <v>636</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>657</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>640</v>
+      </c>
+      <c r="J6" s="40"/>
+      <c r="K6" s="11">
+        <v>2342</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="38"/>
+      <c r="B7" s="35"/>
+      <c r="C7" s="11" t="s">
         <v>619</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D7" s="11" t="s">
+        <v>654</v>
+      </c>
+      <c r="E7" s="11" t="s">
         <v>622</v>
       </c>
-      <c r="E5" s="11" t="s">
-        <v>637</v>
-      </c>
-      <c r="F5" s="11" t="s">
+      <c r="F7" s="41"/>
+      <c r="G7" s="11" t="s">
+        <v>638</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>657</v>
+      </c>
+      <c r="I7" s="11" t="s">
         <v>640</v>
       </c>
-      <c r="G5" s="11">
-        <v>2342</v>
-      </c>
-      <c r="H5" s="34" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="38"/>
-      <c r="B6" s="45"/>
-      <c r="C6" s="11" t="s">
-        <v>619</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>623</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>637</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>641</v>
-      </c>
-      <c r="G6" s="11">
-        <v>2342</v>
-      </c>
-      <c r="H6" s="39"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="37"/>
-      <c r="B7" s="45"/>
-      <c r="C7" s="11" t="s">
-        <v>620</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>623</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>639</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>641</v>
-      </c>
-      <c r="G7" s="11">
+      <c r="J7" s="41"/>
+      <c r="K7" s="11">
         <v>2341</v>
       </c>
-      <c r="H7" s="35"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="36" t="s">
         <v>529</v>
       </c>
-      <c r="B8" s="45"/>
+      <c r="B8" s="35"/>
       <c r="C8" s="11" t="s">
+        <v>618</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>653</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>623</v>
+      </c>
+      <c r="F8" s="39" t="s">
+        <v>530</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>636</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>653</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>639</v>
+      </c>
+      <c r="J8" s="39" t="s">
+        <v>665</v>
+      </c>
+      <c r="K8" s="11"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="37"/>
+      <c r="B9" s="35"/>
+      <c r="C9" s="11" t="s">
+        <v>618</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>654</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>624</v>
+      </c>
+      <c r="F9" s="40"/>
+      <c r="G9" s="11" t="s">
+        <v>636</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>657</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>640</v>
+      </c>
+      <c r="J9" s="40"/>
+      <c r="K9" s="11"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="38"/>
+      <c r="B10" s="35"/>
+      <c r="C10" s="11" t="s">
         <v>619</v>
       </c>
-      <c r="D8" s="11" t="s">
-        <v>624</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>637</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>640</v>
-      </c>
-      <c r="G8" s="11"/>
-      <c r="H8" s="34" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="38"/>
-      <c r="B9" s="45"/>
-      <c r="C9" s="11" t="s">
-        <v>619</v>
-      </c>
-      <c r="D9" s="11" t="s">
+      <c r="D10" s="11" t="s">
+        <v>655</v>
+      </c>
+      <c r="E10" s="11" t="s">
         <v>625</v>
       </c>
-      <c r="E9" s="11" t="s">
-        <v>637</v>
-      </c>
-      <c r="F9" s="11" t="s">
+      <c r="F10" s="41"/>
+      <c r="G10" s="11" t="s">
+        <v>638</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>658</v>
+      </c>
+      <c r="I10" s="11" t="s">
         <v>641</v>
       </c>
-      <c r="G9" s="11"/>
-      <c r="H9" s="39"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="37"/>
-      <c r="B10" s="45"/>
-      <c r="C10" s="11" t="s">
-        <v>620</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>626</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>639</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>642</v>
-      </c>
-      <c r="G10" s="11"/>
-      <c r="H10" s="35"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J10" s="41"/>
+      <c r="K10" s="11"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>531</v>
       </c>
-      <c r="B11" s="45"/>
+      <c r="B11" s="35"/>
       <c r="C11" s="11" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>627</v>
+        <v>656</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>639</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>643</v>
-      </c>
-      <c r="G11" s="11"/>
-      <c r="H11" s="10" t="s">
+        <v>626</v>
+      </c>
+      <c r="F11" s="10" t="s">
         <v>530</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G11" s="11" t="s">
+        <v>638</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>659</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>642</v>
+      </c>
+      <c r="J11" s="10" t="s">
+        <v>665</v>
+      </c>
+      <c r="K11" s="11"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="36" t="s">
         <v>532</v>
       </c>
-      <c r="B12" s="45"/>
+      <c r="B12" s="35"/>
       <c r="C12" s="11" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="D12" s="11" t="s">
+        <v>653</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>627</v>
+      </c>
+      <c r="F12" s="39" t="s">
+        <v>530</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>638</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>653</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>643</v>
+      </c>
+      <c r="J12" s="39" t="s">
+        <v>665</v>
+      </c>
+      <c r="K12" s="11"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="37"/>
+      <c r="B13" s="35"/>
+      <c r="C13" s="11" t="s">
+        <v>619</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>654</v>
+      </c>
+      <c r="E13" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="E12" s="11" t="s">
-        <v>639</v>
-      </c>
-      <c r="F12" s="11" t="s">
+      <c r="F13" s="40"/>
+      <c r="G13" s="11" t="s">
+        <v>638</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>657</v>
+      </c>
+      <c r="I13" s="11" t="s">
         <v>644</v>
       </c>
-      <c r="G12" s="11"/>
-      <c r="H12" s="34" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="38"/>
-      <c r="B13" s="45"/>
-      <c r="C13" s="11" t="s">
-        <v>620</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>629</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>639</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>645</v>
-      </c>
-      <c r="G13" s="11"/>
-      <c r="H13" s="39"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="37"/>
-      <c r="B14" s="45"/>
+      <c r="J13" s="40"/>
+      <c r="K13" s="11"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="38"/>
+      <c r="B14" s="35"/>
       <c r="C14" s="11" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>627</v>
+        <v>656</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>637</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>643</v>
-      </c>
-      <c r="G14" s="11"/>
-      <c r="H14" s="35"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+        <v>626</v>
+      </c>
+      <c r="F14" s="41"/>
+      <c r="G14" s="11" t="s">
+        <v>636</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>659</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>642</v>
+      </c>
+      <c r="J14" s="41"/>
+      <c r="K14" s="11"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="36" t="s">
         <v>533</v>
       </c>
-      <c r="B15" s="45"/>
+      <c r="B15" s="35"/>
       <c r="C15" s="11" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="D15" s="11" t="s">
+        <v>653</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>629</v>
+      </c>
+      <c r="F15" s="39" t="s">
+        <v>530</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>638</v>
+      </c>
+      <c r="H15" s="11" t="s">
+        <v>653</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>645</v>
+      </c>
+      <c r="J15" s="39" t="s">
+        <v>665</v>
+      </c>
+      <c r="K15" s="11"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="37"/>
+      <c r="B16" s="35"/>
+      <c r="C16" s="11" t="s">
+        <v>619</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>654</v>
+      </c>
+      <c r="E16" s="11" t="s">
         <v>630</v>
       </c>
-      <c r="E15" s="11" t="s">
-        <v>639</v>
-      </c>
-      <c r="F15" s="11" t="s">
+      <c r="F16" s="40"/>
+      <c r="G16" s="11" t="s">
+        <v>638</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>657</v>
+      </c>
+      <c r="I16" s="11" t="s">
         <v>646</v>
       </c>
-      <c r="G15" s="11"/>
-      <c r="H15" s="34" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="38"/>
-      <c r="B16" s="45"/>
-      <c r="C16" s="11" t="s">
-        <v>620</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>631</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>639</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>647</v>
-      </c>
-      <c r="G16" s="11"/>
-      <c r="H16" s="39"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="37"/>
-      <c r="B17" s="45"/>
+      <c r="J16" s="40"/>
+      <c r="K16" s="11"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="38"/>
+      <c r="B17" s="35"/>
       <c r="C17" s="11" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>626</v>
+        <v>655</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>637</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>642</v>
-      </c>
-      <c r="G17" s="11"/>
-      <c r="H17" s="35"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+        <v>625</v>
+      </c>
+      <c r="F17" s="41"/>
+      <c r="G17" s="11" t="s">
+        <v>636</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>658</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>641</v>
+      </c>
+      <c r="J17" s="41"/>
+      <c r="K17" s="11"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
         <v>534</v>
       </c>
-      <c r="B18" s="43"/>
+      <c r="B18" s="33"/>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
-      <c r="G18" s="9" t="s">
-        <v>588</v>
-      </c>
+      <c r="G18" s="9"/>
       <c r="H18" s="9"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
         <v>535</v>
       </c>
-      <c r="B19" s="44" t="s">
-        <v>606</v>
+      <c r="B19" s="34" t="s">
+        <v>605</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="D19" s="10" t="s">
+        <v>656</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>615</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>537</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>638</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>659</v>
+      </c>
+      <c r="I19" s="10" t="s">
+        <v>536</v>
+      </c>
+      <c r="J19" s="10" t="s">
+        <v>666</v>
+      </c>
+      <c r="K19" s="10">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="42" t="s">
+        <v>539</v>
+      </c>
+      <c r="B20" s="34"/>
+      <c r="C20" s="10" t="s">
+        <v>619</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>653</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>613</v>
+      </c>
+      <c r="F20" s="39" t="s">
+        <v>540</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>638</v>
+      </c>
+      <c r="H20" s="10" t="s">
+        <v>653</v>
+      </c>
+      <c r="I20" s="10" t="s">
+        <v>588</v>
+      </c>
+      <c r="J20" s="39" t="s">
+        <v>667</v>
+      </c>
+      <c r="K20" s="10">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="43"/>
+      <c r="B21" s="34"/>
+      <c r="C21" s="10" t="s">
+        <v>619</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>654</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>614</v>
+      </c>
+      <c r="F21" s="41"/>
+      <c r="G21" s="10" t="s">
+        <v>638</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>657</v>
+      </c>
+      <c r="I21" s="10" t="s">
+        <v>589</v>
+      </c>
+      <c r="J21" s="41"/>
+      <c r="K21" s="10">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="25" t="s">
+        <v>541</v>
+      </c>
+      <c r="B22" s="34"/>
+      <c r="C22" s="10" t="s">
+        <v>619</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>653</v>
+      </c>
+      <c r="E22" s="10" t="s">
         <v>616</v>
       </c>
-      <c r="E19" s="10" t="s">
-        <v>639</v>
-      </c>
-      <c r="F19" s="10" t="s">
-        <v>536</v>
-      </c>
-      <c r="G19" s="10">
-        <v>841</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="32" t="s">
-        <v>540</v>
-      </c>
-      <c r="B20" s="44"/>
-      <c r="C20" s="10" t="s">
-        <v>620</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>614</v>
-      </c>
-      <c r="E20" s="10" t="s">
-        <v>639</v>
-      </c>
-      <c r="F20" s="10" t="s">
-        <v>589</v>
-      </c>
-      <c r="G20" s="10">
-        <v>842</v>
-      </c>
-      <c r="H20" s="34" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="33"/>
-      <c r="B21" s="44"/>
-      <c r="C21" s="10" t="s">
-        <v>620</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>615</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>639</v>
-      </c>
-      <c r="F21" s="10" t="s">
+      <c r="F22" s="25" t="s">
+        <v>542</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>638</v>
+      </c>
+      <c r="H22" s="10" t="s">
+        <v>653</v>
+      </c>
+      <c r="I22" s="10" t="s">
+        <v>609</v>
+      </c>
+      <c r="J22" s="25" t="s">
+        <v>668</v>
+      </c>
+      <c r="K22" s="10">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="25" t="s">
+        <v>543</v>
+      </c>
+      <c r="B23" s="34"/>
+      <c r="C23" s="10" t="s">
+        <v>619</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>654</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>617</v>
+      </c>
+      <c r="F23" s="25" t="s">
+        <v>544</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>638</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>657</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>608</v>
+      </c>
+      <c r="J23" s="25" t="s">
+        <v>669</v>
+      </c>
+      <c r="K23" s="10">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="36" t="s">
+        <v>545</v>
+      </c>
+      <c r="B24" s="34" t="s">
+        <v>605</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>618</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>653</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>616</v>
+      </c>
+      <c r="F24" s="39" t="s">
+        <v>546</v>
+      </c>
+      <c r="G24" s="10" t="s">
+        <v>636</v>
+      </c>
+      <c r="H24" s="10" t="s">
+        <v>653</v>
+      </c>
+      <c r="I24" s="10" t="s">
         <v>590</v>
       </c>
-      <c r="G21" s="10">
-        <v>843</v>
-      </c>
-      <c r="H21" s="35"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="25" t="s">
+      <c r="J24" s="39" t="s">
+        <v>670</v>
+      </c>
+      <c r="K24" s="10">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="38"/>
+      <c r="B25" s="34" t="s">
+        <v>605</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>618</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>654</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>617</v>
+      </c>
+      <c r="F25" s="41"/>
+      <c r="G25" s="10" t="s">
+        <v>636</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>657</v>
+      </c>
+      <c r="I25" s="10" t="s">
+        <v>591</v>
+      </c>
+      <c r="J25" s="41"/>
+      <c r="K25" s="10">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="25" t="s">
+        <v>547</v>
+      </c>
+      <c r="B26" s="34"/>
+      <c r="C26" s="10" t="s">
+        <v>619</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>656</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>612</v>
+      </c>
+      <c r="F26" s="25" t="s">
+        <v>546</v>
+      </c>
+      <c r="G26" s="10" t="s">
+        <v>638</v>
+      </c>
+      <c r="H26" s="10" t="s">
+        <v>659</v>
+      </c>
+      <c r="I26" s="10" t="s">
+        <v>548</v>
+      </c>
+      <c r="J26" s="25" t="s">
+        <v>670</v>
+      </c>
+      <c r="K26" s="10">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="42" t="s">
+        <v>549</v>
+      </c>
+      <c r="B27" s="34"/>
+      <c r="C27" s="10" t="s">
+        <v>618</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>653</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>631</v>
+      </c>
+      <c r="F27" s="42" t="s">
         <v>542</v>
       </c>
-      <c r="B22" s="44"/>
-      <c r="C22" s="10" t="s">
-        <v>620</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>617</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>639</v>
-      </c>
-      <c r="F22" s="10" t="s">
-        <v>610</v>
-      </c>
-      <c r="G22" s="10">
-        <v>844</v>
-      </c>
-      <c r="H22" s="25" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="25" t="s">
-        <v>544</v>
-      </c>
-      <c r="B23" s="44"/>
-      <c r="C23" s="10" t="s">
-        <v>620</v>
-      </c>
-      <c r="D23" s="10" t="s">
+      <c r="G27" s="10" t="s">
+        <v>636</v>
+      </c>
+      <c r="H27" s="10" t="s">
+        <v>653</v>
+      </c>
+      <c r="I27" s="10" t="s">
+        <v>592</v>
+      </c>
+      <c r="J27" s="42" t="s">
+        <v>668</v>
+      </c>
+      <c r="K27" s="10">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="43"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="10" t="s">
         <v>618</v>
       </c>
-      <c r="E23" s="10" t="s">
-        <v>639</v>
-      </c>
-      <c r="F23" s="10" t="s">
-        <v>609</v>
-      </c>
-      <c r="G23" s="10">
-        <v>845</v>
-      </c>
-      <c r="H23" s="25" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="36" t="s">
-        <v>546</v>
-      </c>
-      <c r="B24" s="44" t="s">
-        <v>606</v>
-      </c>
-      <c r="C24" s="10" t="s">
+      <c r="D28" s="10" t="s">
+        <v>654</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>632</v>
+      </c>
+      <c r="F28" s="43"/>
+      <c r="G28" s="10" t="s">
+        <v>636</v>
+      </c>
+      <c r="H28" s="10" t="s">
+        <v>657</v>
+      </c>
+      <c r="I28" s="10" t="s">
+        <v>593</v>
+      </c>
+      <c r="J28" s="43"/>
+      <c r="K28" s="10">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="25" t="s">
+        <v>550</v>
+      </c>
+      <c r="B29" s="34"/>
+      <c r="C29" s="10" t="s">
         <v>619</v>
       </c>
-      <c r="D24" s="10" t="s">
-        <v>617</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>637</v>
-      </c>
-      <c r="F24" s="10" t="s">
-        <v>591</v>
-      </c>
-      <c r="G24" s="10">
-        <v>847</v>
-      </c>
-      <c r="H24" s="34" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="37"/>
-      <c r="B25" s="44" t="s">
-        <v>606</v>
-      </c>
-      <c r="C25" s="10" t="s">
+      <c r="D29" s="10" t="s">
+        <v>654</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>632</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>674</v>
+      </c>
+      <c r="G29" s="10" t="s">
+        <v>638</v>
+      </c>
+      <c r="H29" s="10" t="s">
+        <v>657</v>
+      </c>
+      <c r="I29" s="10" t="s">
+        <v>551</v>
+      </c>
+      <c r="J29" s="10" t="s">
+        <v>675</v>
+      </c>
+      <c r="K29" s="10">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="25" t="s">
+        <v>552</v>
+      </c>
+      <c r="B30" s="34"/>
+      <c r="C30" s="10" t="s">
         <v>619</v>
       </c>
-      <c r="D25" s="10" t="s">
-        <v>618</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>637</v>
-      </c>
-      <c r="F25" s="10" t="s">
-        <v>592</v>
-      </c>
-      <c r="G25" s="10">
-        <v>848</v>
-      </c>
-      <c r="H25" s="35"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="25" t="s">
-        <v>548</v>
-      </c>
-      <c r="B26" s="44"/>
-      <c r="C26" s="10" t="s">
-        <v>620</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>613</v>
-      </c>
-      <c r="E26" s="10" t="s">
-        <v>639</v>
-      </c>
-      <c r="F26" s="10" t="s">
-        <v>549</v>
-      </c>
-      <c r="G26" s="10">
-        <v>852</v>
-      </c>
-      <c r="H26" s="25" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="32" t="s">
-        <v>550</v>
-      </c>
-      <c r="B27" s="44"/>
-      <c r="C27" s="10" t="s">
-        <v>619</v>
-      </c>
-      <c r="D27" s="10" t="s">
-        <v>632</v>
-      </c>
-      <c r="E27" s="10" t="s">
-        <v>637</v>
-      </c>
-      <c r="F27" s="10" t="s">
-        <v>593</v>
-      </c>
-      <c r="G27" s="10">
-        <v>853</v>
-      </c>
-      <c r="H27" s="32" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="33"/>
-      <c r="B28" s="44"/>
-      <c r="C28" s="10" t="s">
-        <v>619</v>
-      </c>
-      <c r="D28" s="10" t="s">
-        <v>633</v>
-      </c>
-      <c r="E28" s="10" t="s">
-        <v>637</v>
-      </c>
-      <c r="F28" s="10" t="s">
-        <v>594</v>
-      </c>
-      <c r="G28" s="10">
-        <v>854</v>
-      </c>
-      <c r="H28" s="33"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="25" t="s">
-        <v>551</v>
-      </c>
-      <c r="B29" s="44"/>
-      <c r="C29" s="10" t="s">
-        <v>620</v>
-      </c>
-      <c r="D29" s="10" t="s">
-        <v>633</v>
-      </c>
-      <c r="E29" s="10" t="s">
-        <v>639</v>
-      </c>
-      <c r="F29" s="10" t="s">
-        <v>552</v>
-      </c>
-      <c r="G29" s="10">
-        <v>857</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="25" t="s">
-        <v>553</v>
-      </c>
-      <c r="B30" s="44"/>
-      <c r="C30" s="10" t="s">
-        <v>620</v>
-      </c>
       <c r="D30" s="10" t="s">
-        <v>632</v>
+        <v>653</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="F30" s="10" t="s">
         <v>554</v>
       </c>
-      <c r="G30" s="10">
+      <c r="G30" s="10" t="s">
+        <v>638</v>
+      </c>
+      <c r="H30" s="10" t="s">
+        <v>653</v>
+      </c>
+      <c r="I30" s="10" t="s">
+        <v>553</v>
+      </c>
+      <c r="J30" s="10" t="s">
+        <v>671</v>
+      </c>
+      <c r="K30" s="10">
         <v>858</v>
       </c>
-      <c r="H30" s="10" t="s">
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="14" t="s">
+        <v>607</v>
+      </c>
+      <c r="B31" s="34" t="s">
+        <v>605</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>619</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>655</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>633</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>606</v>
+      </c>
+      <c r="G31" s="10" t="s">
+        <v>638</v>
+      </c>
+      <c r="H31" s="10" t="s">
+        <v>658</v>
+      </c>
+      <c r="I31" s="10" t="s">
+        <v>538</v>
+      </c>
+      <c r="J31" s="10" t="s">
+        <v>672</v>
+      </c>
+      <c r="K31" s="10"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="14" t="s">
         <v>555</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" s="14" t="s">
-        <v>608</v>
-      </c>
-      <c r="B31" s="44" t="s">
-        <v>606</v>
-      </c>
-      <c r="C31" s="10" t="s">
+      <c r="B32" s="34" t="s">
+        <v>605</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>619</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>656</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>615</v>
+      </c>
+      <c r="F32" s="10" t="s">
+        <v>556</v>
+      </c>
+      <c r="G32" s="10" t="s">
+        <v>638</v>
+      </c>
+      <c r="H32" s="10" t="s">
+        <v>659</v>
+      </c>
+      <c r="I32" s="10" t="s">
+        <v>536</v>
+      </c>
+      <c r="J32" s="10" t="s">
+        <v>673</v>
+      </c>
+      <c r="K32" s="10">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="44" t="s">
+        <v>557</v>
+      </c>
+      <c r="B33" s="34" t="s">
+        <v>604</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>619</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>653</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>634</v>
+      </c>
+      <c r="F33" s="39" t="s">
+        <v>674</v>
+      </c>
+      <c r="G33" s="10" t="s">
+        <v>638</v>
+      </c>
+      <c r="H33" s="10" t="s">
+        <v>653</v>
+      </c>
+      <c r="I33" s="10" t="s">
+        <v>610</v>
+      </c>
+      <c r="J33" s="39" t="s">
+        <v>675</v>
+      </c>
+      <c r="K33" s="10"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" s="45"/>
+      <c r="B34" s="34" t="s">
+        <v>604</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>619</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>654</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>635</v>
+      </c>
+      <c r="F34" s="41"/>
+      <c r="G34" s="10" t="s">
+        <v>638</v>
+      </c>
+      <c r="H34" s="10" t="s">
+        <v>657</v>
+      </c>
+      <c r="I34" s="10" t="s">
+        <v>611</v>
+      </c>
+      <c r="J34" s="41"/>
+      <c r="K34" s="10"/>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35" s="36" t="s">
+        <v>558</v>
+      </c>
+      <c r="B35" s="34" t="s">
+        <v>605</v>
+      </c>
+      <c r="C35" s="10" t="s">
         <v>620</v>
       </c>
-      <c r="D31" s="10" t="s">
-        <v>634</v>
-      </c>
-      <c r="E31" s="10" t="s">
-        <v>639</v>
-      </c>
-      <c r="F31" s="10" t="s">
-        <v>538</v>
-      </c>
-      <c r="G31" s="10"/>
-      <c r="H31" s="10" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="14" t="s">
-        <v>556</v>
-      </c>
-      <c r="B32" s="44" t="s">
-        <v>606</v>
-      </c>
-      <c r="C32" s="10" t="s">
+      <c r="D35" s="10" t="s">
+        <v>653</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>631</v>
+      </c>
+      <c r="F35" s="39" t="s">
+        <v>674</v>
+      </c>
+      <c r="G35" s="10" t="s">
+        <v>637</v>
+      </c>
+      <c r="H35" s="10" t="s">
+        <v>653</v>
+      </c>
+      <c r="I35" s="10" t="s">
+        <v>594</v>
+      </c>
+      <c r="J35" s="39" t="s">
+        <v>675</v>
+      </c>
+      <c r="K35" s="10">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36" s="38"/>
+      <c r="B36" s="34" t="s">
+        <v>605</v>
+      </c>
+      <c r="C36" s="10" t="s">
         <v>620</v>
       </c>
-      <c r="D32" s="10" t="s">
-        <v>616</v>
-      </c>
-      <c r="E32" s="10" t="s">
-        <v>639</v>
-      </c>
-      <c r="F32" s="10" t="s">
-        <v>536</v>
-      </c>
-      <c r="G32" s="10">
-        <v>862</v>
-      </c>
-      <c r="H32" s="10" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" s="40" t="s">
-        <v>558</v>
-      </c>
-      <c r="B33" s="44" t="s">
+      <c r="D36" s="10" t="s">
+        <v>654</v>
+      </c>
+      <c r="E36" s="10" t="s">
+        <v>632</v>
+      </c>
+      <c r="F36" s="41"/>
+      <c r="G36" s="10" t="s">
+        <v>637</v>
+      </c>
+      <c r="H36" s="10" t="s">
+        <v>657</v>
+      </c>
+      <c r="I36" s="10" t="s">
+        <v>595</v>
+      </c>
+      <c r="J36" s="41"/>
+      <c r="K36" s="10">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37" s="14" t="s">
+        <v>559</v>
+      </c>
+      <c r="B37" s="34" t="s">
         <v>605</v>
       </c>
-      <c r="C33" s="10" t="s">
-        <v>620</v>
-      </c>
-      <c r="D33" s="10" t="s">
-        <v>635</v>
-      </c>
-      <c r="E33" s="10" t="s">
-        <v>639</v>
-      </c>
-      <c r="F33" s="10" t="s">
-        <v>611</v>
-      </c>
-      <c r="G33" s="10"/>
-      <c r="H33" s="34" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="41"/>
-      <c r="B34" s="44" t="s">
-        <v>605</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>620</v>
-      </c>
-      <c r="D34" s="10" t="s">
+      <c r="C37" s="10" t="s">
+        <v>618</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>656</v>
+      </c>
+      <c r="E37" s="10" t="s">
+        <v>612</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>674</v>
+      </c>
+      <c r="G37" s="10" t="s">
         <v>636</v>
       </c>
-      <c r="E34" s="10" t="s">
-        <v>639</v>
-      </c>
-      <c r="F34" s="10" t="s">
-        <v>612</v>
-      </c>
-      <c r="G34" s="10"/>
-      <c r="H34" s="35"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" s="36" t="s">
-        <v>559</v>
-      </c>
-      <c r="B35" s="44" t="s">
-        <v>606</v>
-      </c>
-      <c r="C35" s="10" t="s">
-        <v>621</v>
-      </c>
-      <c r="D35" s="10" t="s">
-        <v>632</v>
-      </c>
-      <c r="E35" s="10" t="s">
-        <v>638</v>
-      </c>
-      <c r="F35" s="10" t="s">
-        <v>595</v>
-      </c>
-      <c r="G35" s="10">
-        <v>859</v>
-      </c>
-      <c r="H35" s="34" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="37"/>
-      <c r="B36" s="44" t="s">
-        <v>606</v>
-      </c>
-      <c r="C36" s="10" t="s">
-        <v>621</v>
-      </c>
-      <c r="D36" s="10" t="s">
-        <v>633</v>
-      </c>
-      <c r="E36" s="10" t="s">
-        <v>638</v>
-      </c>
-      <c r="F36" s="10" t="s">
-        <v>596</v>
-      </c>
-      <c r="G36" s="10">
-        <v>860</v>
-      </c>
-      <c r="H36" s="35"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="14" t="s">
+      <c r="H37" s="10" t="s">
+        <v>659</v>
+      </c>
+      <c r="I37" s="10" t="s">
         <v>560</v>
       </c>
-      <c r="B37" s="44" t="s">
-        <v>606</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>619</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>613</v>
-      </c>
-      <c r="E37" s="10" t="s">
-        <v>637</v>
-      </c>
-      <c r="F37" s="10" t="s">
-        <v>561</v>
-      </c>
-      <c r="G37" s="10">
+      <c r="J37" s="10" t="s">
+        <v>675</v>
+      </c>
+      <c r="K37" s="10">
         <v>861</v>
       </c>
-      <c r="H37" s="10" t="s">
-        <v>539</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="H5:H7"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="H8:H10"/>
-    <mergeCell ref="A12:A14"/>
-    <mergeCell ref="H12:H14"/>
+  <mergeCells count="27">
+    <mergeCell ref="F33:F34"/>
+    <mergeCell ref="F35:F36"/>
     <mergeCell ref="A27:A28"/>
-    <mergeCell ref="H27:H28"/>
-    <mergeCell ref="H35:H36"/>
+    <mergeCell ref="J27:J28"/>
+    <mergeCell ref="J35:J36"/>
     <mergeCell ref="A35:A36"/>
     <mergeCell ref="A15:A17"/>
-    <mergeCell ref="H15:H17"/>
+    <mergeCell ref="J15:J17"/>
     <mergeCell ref="A20:A21"/>
-    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="J20:J21"/>
     <mergeCell ref="A24:A25"/>
-    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="J24:J25"/>
     <mergeCell ref="A33:A34"/>
-    <mergeCell ref="H33:H34"/>
+    <mergeCell ref="J33:J34"/>
+    <mergeCell ref="F15:F17"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="F27:F28"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="J5:J7"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="J8:J10"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="J12:J14"/>
+    <mergeCell ref="F5:F7"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="F12:F14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3519,25 +3916,25 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF19D07F-C891-4FD7-A451-C71533DD2DA9}">
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.109375" customWidth="1"/>
-    <col min="2" max="2" width="14.5546875" customWidth="1"/>
-    <col min="3" max="3" width="31.109375" customWidth="1"/>
-    <col min="4" max="4" width="12.5546875" customWidth="1"/>
-    <col min="5" max="5" width="29.5546875" customWidth="1"/>
-    <col min="6" max="6" width="20.6640625" customWidth="1"/>
-    <col min="7" max="7" width="17.109375" customWidth="1"/>
-    <col min="8" max="8" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.140625" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" customWidth="1"/>
+    <col min="3" max="3" width="31.140625" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" customWidth="1"/>
+    <col min="5" max="5" width="29.5703125" customWidth="1"/>
+    <col min="6" max="6" width="20.7109375" customWidth="1"/>
+    <col min="7" max="7" width="17.140625" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="20" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
         <v>472</v>
       </c>
@@ -3560,7 +3957,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>511</v>
       </c>
@@ -3571,7 +3968,7 @@
         <v>512</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="E3" s="16" t="s">
         <v>514</v>
@@ -3580,10 +3977,10 @@
         <v>513</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
         <v>488</v>
       </c>
@@ -3594,7 +3991,7 @@
         <v>489</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="E4" s="19" t="s">
         <v>491</v>
@@ -3603,10 +4000,10 @@
         <v>490</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
         <v>502</v>
       </c>
@@ -3617,7 +4014,7 @@
         <v>503</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E5" s="16" t="s">
         <v>505</v>
@@ -3626,10 +4023,10 @@
         <v>504</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>497</v>
       </c>
@@ -3640,7 +4037,7 @@
         <v>498</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E6" s="16" t="s">
         <v>501</v>
@@ -3649,10 +4046,10 @@
         <v>500</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>506</v>
       </c>
@@ -3663,7 +4060,7 @@
         <v>508</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E7" s="16" t="s">
         <v>510</v>
@@ -3672,15 +4069,15 @@
         <v>509</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="20" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="18" t="s">
         <v>472</v>
       </c>
@@ -3694,16 +4091,16 @@
         <v>476</v>
       </c>
       <c r="E9" s="18" t="s">
+        <v>574</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>582</v>
+      </c>
+      <c r="G9" s="18" t="s">
         <v>575</v>
       </c>
-      <c r="F9" s="18" t="s">
-        <v>583</v>
-      </c>
-      <c r="G9" s="18" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
         <v>515</v>
       </c>
@@ -3714,19 +4111,19 @@
         <v>516</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F10" s="16" t="s">
         <v>517</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
         <v>492</v>
       </c>
@@ -3737,19 +4134,19 @@
         <v>494</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="F11" s="16" t="s">
         <v>495</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
         <v>519</v>
       </c>
@@ -3760,19 +4157,19 @@
         <v>516</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="F12" s="16" t="s">
         <v>520</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
         <v>482</v>
       </c>
@@ -3783,16 +4180,16 @@
         <v>484</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="F13" s="16" t="s">
         <v>486</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
   </sheetData>
@@ -3803,16 +4200,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02100B6D-FE78-4CA2-BE15-61CB2638D07F}">
   <dimension ref="A1:D89"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.33203125" style="28" customWidth="1"/>
-    <col min="2" max="2" width="49.5546875" style="28" customWidth="1"/>
-    <col min="3" max="3" width="20.5546875" style="28" customWidth="1"/>
-    <col min="4" max="4" width="38.44140625" style="28" customWidth="1"/>
-    <col min="5" max="16384" width="8.88671875" style="28"/>
+    <col min="1" max="1" width="34.28515625" style="28" customWidth="1"/>
+    <col min="2" max="2" width="49.5703125" style="28" customWidth="1"/>
+    <col min="3" max="3" width="20.5703125" style="28" customWidth="1"/>
+    <col min="4" max="4" width="38.42578125" style="28" customWidth="1"/>
+    <col min="5" max="16384" width="8.85546875" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
         <v>253</v>
       </c>
@@ -3826,7 +4223,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="29" t="s">
         <v>83</v>
       </c>
@@ -3840,7 +4237,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="30" t="s">
         <v>86</v>
       </c>
@@ -3852,7 +4249,7 @@
       </c>
       <c r="D3" s="4"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="30" t="s">
         <v>278</v>
       </c>
@@ -3864,7 +4261,7 @@
       </c>
       <c r="D4" s="4"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="29" t="s">
         <v>244</v>
       </c>
@@ -3878,7 +4275,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="29" t="s">
         <v>245</v>
       </c>
@@ -3892,7 +4289,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="29" t="s">
         <v>243</v>
       </c>
@@ -3906,7 +4303,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="30" t="s">
         <v>344</v>
       </c>
@@ -3918,7 +4315,7 @@
       </c>
       <c r="D8" s="4"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="29" t="s">
         <v>246</v>
       </c>
@@ -3929,10 +4326,10 @@
         <v>389</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="30" t="s">
         <v>260</v>
       </c>
@@ -3946,7 +4343,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="30" t="s">
         <v>228</v>
       </c>
@@ -3960,7 +4357,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="30" t="s">
         <v>3</v>
       </c>
@@ -3974,7 +4371,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="30" t="s">
         <v>5</v>
       </c>
@@ -3988,7 +4385,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="30" t="s">
         <v>229</v>
       </c>
@@ -4002,7 +4399,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="30" t="s">
         <v>9</v>
       </c>
@@ -4016,7 +4413,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="30" t="s">
         <v>53</v>
       </c>
@@ -4030,7 +4427,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="30" t="s">
         <v>230</v>
       </c>
@@ -4044,7 +4441,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="30" t="s">
         <v>231</v>
       </c>
@@ -4058,7 +4455,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="30" t="s">
         <v>289</v>
       </c>
@@ -4072,7 +4469,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="30" t="s">
         <v>19</v>
       </c>
@@ -4086,7 +4483,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="30" t="s">
         <v>23</v>
       </c>
@@ -4100,7 +4497,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="30" t="s">
         <v>232</v>
       </c>
@@ -4114,7 +4511,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="30" t="s">
         <v>233</v>
       </c>
@@ -4128,7 +4525,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="30" t="s">
         <v>298</v>
       </c>
@@ -4142,7 +4539,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="30" t="s">
         <v>116</v>
       </c>
@@ -4156,7 +4553,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="30" t="s">
         <v>306</v>
       </c>
@@ -4170,7 +4567,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="30" t="s">
         <v>310</v>
       </c>
@@ -4184,7 +4581,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="30" t="s">
         <v>235</v>
       </c>
@@ -4198,7 +4595,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="30" t="s">
         <v>40</v>
       </c>
@@ -4212,7 +4609,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="30" t="s">
         <v>236</v>
       </c>
@@ -4226,7 +4623,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="30" t="s">
         <v>319</v>
       </c>
@@ -4238,7 +4635,7 @@
       </c>
       <c r="D31" s="4"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="30" t="s">
         <v>44</v>
       </c>
@@ -4252,7 +4649,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="30" t="s">
         <v>237</v>
       </c>
@@ -4266,7 +4663,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="30" t="s">
         <v>333</v>
       </c>
@@ -4280,7 +4677,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="30" t="s">
         <v>238</v>
       </c>
@@ -4294,7 +4691,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="30" t="s">
         <v>239</v>
       </c>
@@ -4308,7 +4705,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="30" t="s">
         <v>350</v>
       </c>
@@ -4322,7 +4719,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="30" t="s">
         <v>234</v>
       </c>
@@ -4336,7 +4733,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="30" t="s">
         <v>357</v>
       </c>
@@ -4350,7 +4747,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="30" t="s">
         <v>363</v>
       </c>
@@ -4364,7 +4761,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="30" t="s">
         <v>365</v>
       </c>
@@ -4378,7 +4775,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="30" t="s">
         <v>367</v>
       </c>
@@ -4392,7 +4789,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="30" t="s">
         <v>240</v>
       </c>
@@ -4406,7 +4803,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="30" t="s">
         <v>370</v>
       </c>
@@ -4420,7 +4817,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="30" t="s">
         <v>241</v>
       </c>
@@ -4434,7 +4831,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="30" t="s">
         <v>376</v>
       </c>
@@ -4448,7 +4845,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="30" t="s">
         <v>242</v>
       </c>
@@ -4462,7 +4859,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="30" t="s">
         <v>381</v>
       </c>
@@ -4476,7 +4873,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="30" t="s">
         <v>98</v>
       </c>
@@ -4490,7 +4887,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="30" t="s">
         <v>258</v>
       </c>
@@ -4504,7 +4901,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="30" t="s">
         <v>263</v>
       </c>
@@ -4518,7 +4915,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="30" t="s">
         <v>100</v>
       </c>
@@ -4532,7 +4929,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="30" t="s">
         <v>271</v>
       </c>
@@ -4546,7 +4943,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="30" t="s">
         <v>274</v>
       </c>
@@ -4560,7 +4957,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="30" t="s">
         <v>276</v>
       </c>
@@ -4574,7 +4971,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="30" t="s">
         <v>107</v>
       </c>
@@ -4588,7 +4985,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="30" t="s">
         <v>217</v>
       </c>
@@ -4602,7 +4999,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="30" t="s">
         <v>285</v>
       </c>
@@ -4616,7 +5013,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="30" t="s">
         <v>252</v>
       </c>
@@ -4630,7 +5027,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="30" t="s">
         <v>109</v>
       </c>
@@ -4642,7 +5039,7 @@
       </c>
       <c r="D60" s="4"/>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="30" t="s">
         <v>112</v>
       </c>
@@ -4656,7 +5053,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="30" t="s">
         <v>301</v>
       </c>
@@ -4668,7 +5065,7 @@
       </c>
       <c r="D62" s="4"/>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="30" t="s">
         <v>215</v>
       </c>
@@ -4682,7 +5079,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="30" t="s">
         <v>247</v>
       </c>
@@ -4696,7 +5093,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="30" t="s">
         <v>308</v>
       </c>
@@ -4708,7 +5105,7 @@
       </c>
       <c r="D65" s="4"/>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="30" t="s">
         <v>313</v>
       </c>
@@ -4722,7 +5119,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="30" t="s">
         <v>315</v>
       </c>
@@ -4736,7 +5133,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="30" t="s">
         <v>321</v>
       </c>
@@ -4750,7 +5147,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="30" t="s">
         <v>213</v>
       </c>
@@ -4762,7 +5159,7 @@
       </c>
       <c r="D69" s="4"/>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="30" t="s">
         <v>325</v>
       </c>
@@ -4776,7 +5173,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="30" t="s">
         <v>328</v>
       </c>
@@ -4790,7 +5187,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="30" t="s">
         <v>126</v>
       </c>
@@ -4804,7 +5201,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="30" t="s">
         <v>331</v>
       </c>
@@ -4818,7 +5215,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="30" t="s">
         <v>335</v>
       </c>
@@ -4832,7 +5229,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="30" t="s">
         <v>338</v>
       </c>
@@ -4846,7 +5243,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="30" t="s">
         <v>248</v>
       </c>
@@ -4860,7 +5257,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="30" t="s">
         <v>342</v>
       </c>
@@ -4872,7 +5269,7 @@
       </c>
       <c r="D77" s="4"/>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="30" t="s">
         <v>249</v>
       </c>
@@ -4886,7 +5283,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="30" t="s">
         <v>348</v>
       </c>
@@ -4900,7 +5297,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="30" t="s">
         <v>352</v>
       </c>
@@ -4914,7 +5311,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="30" t="s">
         <v>355</v>
       </c>
@@ -4928,7 +5325,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="30" t="s">
         <v>359</v>
       </c>
@@ -4942,7 +5339,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="30" t="s">
         <v>361</v>
       </c>
@@ -4956,7 +5353,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="30" t="s">
         <v>251</v>
       </c>
@@ -4970,7 +5367,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="30" t="s">
         <v>374</v>
       </c>
@@ -4984,7 +5381,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="30" t="s">
         <v>378</v>
       </c>
@@ -4998,7 +5395,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="30" t="s">
         <v>383</v>
       </c>
@@ -5012,7 +5409,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="30" t="s">
         <v>385</v>
       </c>
@@ -5026,7 +5423,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="30" t="s">
         <v>250</v>
       </c>
@@ -5133,17 +5530,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D2DE0FD-72B8-47D0-8668-3E63A2804089}">
   <dimension ref="A1:B155"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="35.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="35.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>226</v>
       </c>
@@ -5151,7 +5548,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -5159,7 +5556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
@@ -5167,7 +5564,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
@@ -5175,7 +5572,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -5183,7 +5580,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -5191,7 +5588,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
@@ -5199,7 +5596,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
@@ -5207,7 +5604,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
@@ -5215,7 +5612,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
@@ -5223,7 +5620,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>15</v>
       </c>
@@ -5231,7 +5628,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
@@ -5239,7 +5636,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
@@ -5247,7 +5644,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>21</v>
       </c>
@@ -5255,7 +5652,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>23</v>
       </c>
@@ -5263,7 +5660,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>25</v>
       </c>
@@ -5271,7 +5668,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>27</v>
       </c>
@@ -5279,7 +5676,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>29</v>
       </c>
@@ -5287,7 +5684,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>31</v>
       </c>
@@ -5295,7 +5692,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>32</v>
       </c>
@@ -5303,7 +5700,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>33</v>
       </c>
@@ -5311,7 +5708,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>35</v>
       </c>
@@ -5319,7 +5716,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>36</v>
       </c>
@@ -5327,7 +5724,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>37</v>
       </c>
@@ -5335,7 +5732,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>39</v>
       </c>
@@ -5343,7 +5740,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>40</v>
       </c>
@@ -5351,7 +5748,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>42</v>
       </c>
@@ -5359,7 +5756,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>44</v>
       </c>
@@ -5367,7 +5764,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>46</v>
       </c>
@@ -5375,7 +5772,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>47</v>
       </c>
@@ -5383,7 +5780,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>48</v>
       </c>
@@ -5391,7 +5788,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>49</v>
       </c>
@@ -5399,7 +5796,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>50</v>
       </c>
@@ -5407,7 +5804,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>51</v>
       </c>
@@ -5415,7 +5812,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>53</v>
       </c>
@@ -5423,7 +5820,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>55</v>
       </c>
@@ -5431,7 +5828,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>56</v>
       </c>
@@ -5439,7 +5836,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>57</v>
       </c>
@@ -5447,7 +5844,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>59</v>
       </c>
@@ -5455,7 +5852,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>60</v>
       </c>
@@ -5463,7 +5860,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>61</v>
       </c>
@@ -5471,7 +5868,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>62</v>
       </c>
@@ -5479,7 +5876,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>64</v>
       </c>
@@ -5487,7 +5884,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>65</v>
       </c>
@@ -5495,7 +5892,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>67</v>
       </c>
@@ -5503,7 +5900,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>68</v>
       </c>
@@ -5511,7 +5908,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>69</v>
       </c>
@@ -5519,7 +5916,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>71</v>
       </c>
@@ -5527,7 +5924,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>73</v>
       </c>
@@ -5535,7 +5932,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>75</v>
       </c>
@@ -5543,7 +5940,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>76</v>
       </c>
@@ -5551,7 +5948,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>78</v>
       </c>
@@ -5559,7 +5956,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>79</v>
       </c>
@@ -5567,7 +5964,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>81</v>
       </c>
@@ -5575,7 +5972,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>83</v>
       </c>
@@ -5583,7 +5980,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>85</v>
       </c>
@@ -5591,7 +5988,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>86</v>
       </c>
@@ -5599,7 +5996,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>88</v>
       </c>
@@ -5607,7 +6004,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>89</v>
       </c>
@@ -5615,7 +6012,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>90</v>
       </c>
@@ -5623,7 +6020,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>91</v>
       </c>
@@ -5631,7 +6028,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>86</v>
       </c>
@@ -5639,7 +6036,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>92</v>
       </c>
@@ -5647,7 +6044,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>92</v>
       </c>
@@ -5655,7 +6052,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>95</v>
       </c>
@@ -5663,7 +6060,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>97</v>
       </c>
@@ -5671,7 +6068,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>98</v>
       </c>
@@ -5679,7 +6076,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>100</v>
       </c>
@@ -5687,7 +6084,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>102</v>
       </c>
@@ -5695,7 +6092,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>103</v>
       </c>
@@ -5703,7 +6100,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>104</v>
       </c>
@@ -5711,7 +6108,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>106</v>
       </c>
@@ -5719,7 +6116,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>107</v>
       </c>
@@ -5727,7 +6124,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>109</v>
       </c>
@@ -5735,7 +6132,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>111</v>
       </c>
@@ -5743,7 +6140,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>112</v>
       </c>
@@ -5751,7 +6148,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>114</v>
       </c>
@@ -5759,7 +6156,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>116</v>
       </c>
@@ -5767,7 +6164,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>118</v>
       </c>
@@ -5775,7 +6172,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>119</v>
       </c>
@@ -5783,7 +6180,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>120</v>
       </c>
@@ -5791,7 +6188,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>121</v>
       </c>
@@ -5799,7 +6196,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>123</v>
       </c>
@@ -5807,7 +6204,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>125</v>
       </c>
@@ -5815,7 +6212,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>126</v>
       </c>
@@ -5823,7 +6220,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>128</v>
       </c>
@@ -5831,7 +6228,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>129</v>
       </c>
@@ -5839,7 +6236,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>130</v>
       </c>
@@ -5847,7 +6244,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>131</v>
       </c>
@@ -5855,7 +6252,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>132</v>
       </c>
@@ -5863,7 +6260,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>133</v>
       </c>
@@ -5871,7 +6268,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>134</v>
       </c>
@@ -5879,7 +6276,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>135</v>
       </c>
@@ -5887,7 +6284,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>137</v>
       </c>
@@ -5895,7 +6292,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>138</v>
       </c>
@@ -5903,7 +6300,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>139</v>
       </c>
@@ -5911,7 +6308,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>140</v>
       </c>
@@ -5919,7 +6316,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>141</v>
       </c>
@@ -5927,7 +6324,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>142</v>
       </c>
@@ -5935,7 +6332,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>143</v>
       </c>
@@ -5943,7 +6340,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>144</v>
       </c>
@@ -5951,7 +6348,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>145</v>
       </c>
@@ -5959,7 +6356,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>147</v>
       </c>
@@ -5967,7 +6364,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>148</v>
       </c>
@@ -5975,7 +6372,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>149</v>
       </c>
@@ -5983,7 +6380,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>150</v>
       </c>
@@ -5991,7 +6388,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>152</v>
       </c>
@@ -5999,7 +6396,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>153</v>
       </c>
@@ -6007,7 +6404,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>154</v>
       </c>
@@ -6015,7 +6412,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>156</v>
       </c>
@@ -6023,7 +6420,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>157</v>
       </c>
@@ -6031,7 +6428,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>159</v>
       </c>
@@ -6039,7 +6436,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>161</v>
       </c>
@@ -6047,7 +6444,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>163</v>
       </c>
@@ -6055,7 +6452,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>165</v>
       </c>
@@ -6063,7 +6460,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>167</v>
       </c>
@@ -6071,7 +6468,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>169</v>
       </c>
@@ -6079,7 +6476,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>170</v>
       </c>
@@ -6087,7 +6484,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>171</v>
       </c>
@@ -6095,7 +6492,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>172</v>
       </c>
@@ -6103,7 +6500,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>173</v>
       </c>
@@ -6111,7 +6508,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>174</v>
       </c>
@@ -6119,7 +6516,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>176</v>
       </c>
@@ -6127,7 +6524,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>177</v>
       </c>
@@ -6135,7 +6532,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>178</v>
       </c>
@@ -6143,7 +6540,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>179</v>
       </c>
@@ -6151,7 +6548,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>181</v>
       </c>
@@ -6159,7 +6556,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>182</v>
       </c>
@@ -6167,7 +6564,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>183</v>
       </c>
@@ -6175,7 +6572,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>183</v>
       </c>
@@ -6183,7 +6580,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>186</v>
       </c>
@@ -6191,7 +6588,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>188</v>
       </c>
@@ -6199,7 +6596,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>190</v>
       </c>
@@ -6207,7 +6604,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>191</v>
       </c>
@@ -6215,7 +6612,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>193</v>
       </c>
@@ -6223,7 +6620,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>195</v>
       </c>
@@ -6231,7 +6628,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>197</v>
       </c>
@@ -6239,7 +6636,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>199</v>
       </c>
@@ -6247,7 +6644,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>201</v>
       </c>
@@ -6255,7 +6652,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>100</v>
       </c>
@@ -6263,7 +6660,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>204</v>
       </c>
@@ -6271,7 +6668,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>206</v>
       </c>
@@ -6279,7 +6676,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>208</v>
       </c>
@@ -6287,7 +6684,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>210</v>
       </c>
@@ -6295,7 +6692,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>211</v>
       </c>
@@ -6303,7 +6700,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>212</v>
       </c>
@@ -6311,7 +6708,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>213</v>
       </c>
@@ -6319,7 +6716,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>215</v>
       </c>
@@ -6327,7 +6724,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>217</v>
       </c>
@@ -6335,7 +6732,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>219</v>
       </c>
@@ -6343,7 +6740,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>220</v>
       </c>
@@ -6351,7 +6748,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>222</v>
       </c>
@@ -6359,7 +6756,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>224</v>
       </c>
@@ -6376,25 +6773,25 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E488C0EA-2C28-4978-995C-65490886A988}">
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.44140625" style="21" customWidth="1"/>
-    <col min="5" max="6" width="11.33203125" customWidth="1"/>
+    <col min="1" max="1" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" style="21" customWidth="1"/>
+    <col min="5" max="6" width="11.28515625" customWidth="1"/>
     <col min="7" max="7" width="16" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.7109375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="20" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
         <v>472</v>
       </c>
@@ -6405,7 +6802,7 @@
         <v>474</v>
       </c>
       <c r="D2" s="22" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="E2" s="18" t="s">
         <v>475</v>
@@ -6429,7 +6826,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>497</v>
       </c>
@@ -6460,7 +6857,7 @@
       <c r="J3" s="16"/>
       <c r="K3" s="16"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
         <v>502</v>
       </c>
@@ -6491,7 +6888,7 @@
       <c r="J4" s="16"/>
       <c r="K4" s="16"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
         <v>506</v>
       </c>
@@ -6502,7 +6899,7 @@
         <v>508</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="E5" s="16" t="s">
         <v>499</v>
@@ -6522,7 +6919,7 @@
       <c r="J5" s="16"/>
       <c r="K5" s="16"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>511</v>
       </c>
@@ -6553,12 +6950,12 @@
       <c r="J6" s="16"/>
       <c r="K6" s="16"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="20" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
         <v>472</v>
       </c>
@@ -6569,7 +6966,7 @@
         <v>474</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="E8" s="18" t="s">
         <v>475</v>
@@ -6593,7 +6990,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
         <v>482</v>
       </c>
@@ -6624,7 +7021,7 @@
       <c r="J9" s="16"/>
       <c r="K9" s="16"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
         <v>488</v>
       </c>
@@ -6655,7 +7052,7 @@
       <c r="J10" s="16"/>
       <c r="K10" s="16"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
         <v>492</v>
       </c>
@@ -6686,7 +7083,7 @@
       <c r="J11" s="16"/>
       <c r="K11" s="16"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
         <v>515</v>
       </c>
@@ -6717,7 +7114,7 @@
       <c r="J12" s="16"/>
       <c r="K12" s="16"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
         <v>519</v>
       </c>
